--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>CSTM</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8810200</v>
+        <v>7876800</v>
       </c>
       <c r="E8" s="3">
-        <v>6674900</v>
+        <v>8835400</v>
       </c>
       <c r="F8" s="3">
-        <v>5298100</v>
+        <v>6694000</v>
       </c>
       <c r="G8" s="3">
-        <v>6409100</v>
+        <v>5313200</v>
       </c>
       <c r="H8" s="3">
-        <v>6169300</v>
+        <v>6427400</v>
       </c>
       <c r="I8" s="3">
-        <v>5682100</v>
+        <v>6186900</v>
       </c>
       <c r="J8" s="3">
+        <v>5698400</v>
+      </c>
+      <c r="K8" s="3">
         <v>5146200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5260200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4139300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4180700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3963800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4174100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8081100</v>
+        <v>7104200</v>
       </c>
       <c r="E9" s="3">
-        <v>5954500</v>
+        <v>8104200</v>
       </c>
       <c r="F9" s="3">
-        <v>4766400</v>
+        <v>5971500</v>
       </c>
       <c r="G9" s="3">
-        <v>5755900</v>
+        <v>4780000</v>
       </c>
       <c r="H9" s="3">
-        <v>5585600</v>
+        <v>5772400</v>
       </c>
       <c r="I9" s="3">
-        <v>5097300</v>
+        <v>5601500</v>
       </c>
       <c r="J9" s="3">
+        <v>5111900</v>
+      </c>
+      <c r="K9" s="3">
         <v>4586300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4800800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3593900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3617300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6882300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7599200</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>729100</v>
+        <v>772600</v>
       </c>
       <c r="E10" s="3">
-        <v>720400</v>
+        <v>731200</v>
       </c>
       <c r="F10" s="3">
-        <v>531700</v>
+        <v>722500</v>
       </c>
       <c r="G10" s="3">
-        <v>653200</v>
+        <v>533200</v>
       </c>
       <c r="H10" s="3">
-        <v>583700</v>
+        <v>655000</v>
       </c>
       <c r="I10" s="3">
-        <v>584800</v>
+        <v>585400</v>
       </c>
       <c r="J10" s="3">
+        <v>586500</v>
+      </c>
+      <c r="K10" s="3">
         <v>559900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>459400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>545400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>563400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2918500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-3425200</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>46700</v>
+        <v>56600</v>
       </c>
       <c r="E12" s="3">
-        <v>36900</v>
+        <v>46800</v>
       </c>
       <c r="F12" s="3">
-        <v>36900</v>
+        <v>37000</v>
       </c>
       <c r="G12" s="3">
-        <v>45600</v>
+        <v>37000</v>
       </c>
       <c r="H12" s="3">
-        <v>39100</v>
+        <v>45700</v>
       </c>
       <c r="I12" s="3">
-        <v>35800</v>
+        <v>39200</v>
       </c>
       <c r="J12" s="3">
+        <v>35900</v>
+      </c>
+      <c r="K12" s="3">
         <v>34700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>42900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>43100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>39500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>38700</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-49900</v>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E14" s="3">
-        <v>67300</v>
+        <v>-50100</v>
       </c>
       <c r="F14" s="3">
-        <v>69400</v>
+        <v>67500</v>
       </c>
       <c r="G14" s="3">
+        <v>69600</v>
+      </c>
+      <c r="H14" s="3">
         <v>3300</v>
       </c>
-      <c r="H14" s="3">
-        <v>-38000</v>
-      </c>
       <c r="I14" s="3">
-        <v>81400</v>
+        <v>-38100</v>
       </c>
       <c r="J14" s="3">
+        <v>81600</v>
+      </c>
+      <c r="K14" s="3">
         <v>5400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>479800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>45200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>27500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23500</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3">
-        <v>18400</v>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E15" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F15" s="3">
         <v>23900</v>
       </c>
-      <c r="F15" s="3">
-        <v>20600</v>
-      </c>
       <c r="G15" s="3">
-        <v>20600</v>
+        <v>20700</v>
       </c>
       <c r="H15" s="3">
+        <v>20700</v>
+      </c>
+      <c r="I15" s="3">
         <v>14100</v>
       </c>
-      <c r="I15" s="3">
-        <v>11900</v>
-      </c>
       <c r="J15" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K15" s="3">
         <v>8700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6600</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8447800</v>
+        <v>7510100</v>
       </c>
       <c r="E17" s="3">
-        <v>6179100</v>
+        <v>8471900</v>
       </c>
       <c r="F17" s="3">
-        <v>5162400</v>
+        <v>6196700</v>
       </c>
       <c r="G17" s="3">
-        <v>6132400</v>
+        <v>5177200</v>
       </c>
       <c r="H17" s="3">
-        <v>5731000</v>
+        <v>6149900</v>
       </c>
       <c r="I17" s="3">
-        <v>5432600</v>
+        <v>5747300</v>
       </c>
       <c r="J17" s="3">
+        <v>5448100</v>
+      </c>
+      <c r="K17" s="3">
         <v>4879200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5695000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3969900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3930700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3675000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4248000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>362400</v>
+        <v>366700</v>
       </c>
       <c r="E18" s="3">
-        <v>495800</v>
+        <v>363400</v>
       </c>
       <c r="F18" s="3">
-        <v>135600</v>
+        <v>497300</v>
       </c>
       <c r="G18" s="3">
-        <v>276700</v>
+        <v>136000</v>
       </c>
       <c r="H18" s="3">
-        <v>438300</v>
+        <v>277500</v>
       </c>
       <c r="I18" s="3">
-        <v>249500</v>
+        <v>439600</v>
       </c>
       <c r="J18" s="3">
+        <v>250300</v>
+      </c>
+      <c r="K18" s="3">
         <v>266900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-434900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>169400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>250000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>288800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-74000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11900</v>
+        <v>-153400</v>
       </c>
       <c r="E20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-9800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4300</v>
-      </c>
       <c r="H20" s="3">
-        <v>-38000</v>
+        <v>-4400</v>
       </c>
       <c r="I20" s="3">
-        <v>-10800</v>
+        <v>-38100</v>
       </c>
       <c r="J20" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K20" s="3">
         <v>3300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-87300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-70300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-160800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>661700</v>
+        <v>535100</v>
       </c>
       <c r="E21" s="3">
-        <v>775700</v>
+        <v>665600</v>
       </c>
       <c r="F21" s="3">
-        <v>399200</v>
+        <v>779700</v>
       </c>
       <c r="G21" s="3">
-        <v>550000</v>
+        <v>402100</v>
       </c>
       <c r="H21" s="3">
-        <v>614000</v>
+        <v>553300</v>
       </c>
       <c r="I21" s="3">
-        <v>424200</v>
+        <v>617100</v>
       </c>
       <c r="J21" s="3">
+        <v>426600</v>
+      </c>
+      <c r="K21" s="3">
         <v>438300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-286500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>210100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>200800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>233900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-232400</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>130200</v>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E22" s="3">
-        <v>142100</v>
+        <v>130600</v>
       </c>
       <c r="F22" s="3">
-        <v>155200</v>
+        <v>142500</v>
       </c>
       <c r="G22" s="3">
-        <v>183400</v>
+        <v>155600</v>
       </c>
       <c r="H22" s="3">
-        <v>159500</v>
+        <v>183900</v>
       </c>
       <c r="I22" s="3">
-        <v>185500</v>
+        <v>160000</v>
       </c>
       <c r="J22" s="3">
+        <v>186100</v>
+      </c>
+      <c r="K22" s="3">
         <v>199600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>169500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>220300</v>
+        <v>213300</v>
       </c>
       <c r="E23" s="3">
-        <v>343900</v>
+        <v>220900</v>
       </c>
       <c r="F23" s="3">
-        <v>-36900</v>
+        <v>344900</v>
       </c>
       <c r="G23" s="3">
-        <v>89000</v>
+        <v>-37000</v>
       </c>
       <c r="H23" s="3">
-        <v>240900</v>
+        <v>89200</v>
       </c>
       <c r="I23" s="3">
-        <v>53200</v>
+        <v>241600</v>
       </c>
       <c r="J23" s="3">
+        <v>53300</v>
+      </c>
+      <c r="K23" s="3">
         <v>70500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-596100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>102700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>161500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>214100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-239500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-113900</v>
+        <v>72900</v>
       </c>
       <c r="E24" s="3">
-        <v>59700</v>
+        <v>-114300</v>
       </c>
       <c r="F24" s="3">
-        <v>-18400</v>
+        <v>59800</v>
       </c>
       <c r="G24" s="3">
-        <v>19500</v>
+        <v>-18500</v>
       </c>
       <c r="H24" s="3">
-        <v>34700</v>
+        <v>19600</v>
       </c>
       <c r="I24" s="3">
-        <v>104200</v>
+        <v>34800</v>
       </c>
       <c r="J24" s="3">
+        <v>104500</v>
+      </c>
+      <c r="K24" s="3">
         <v>74900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-32700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>41800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>50500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-39900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>334200</v>
+        <v>140400</v>
       </c>
       <c r="E26" s="3">
-        <v>284300</v>
+        <v>335100</v>
       </c>
       <c r="F26" s="3">
-        <v>-18400</v>
+        <v>285100</v>
       </c>
       <c r="G26" s="3">
-        <v>69400</v>
+        <v>-18500</v>
       </c>
       <c r="H26" s="3">
-        <v>206200</v>
+        <v>69600</v>
       </c>
       <c r="I26" s="3">
-        <v>-51000</v>
+        <v>206700</v>
       </c>
       <c r="J26" s="3">
+        <v>-51100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-563500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>61000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>114800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>163600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-199500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>326600</v>
+        <v>136000</v>
       </c>
       <c r="E27" s="3">
-        <v>278800</v>
+        <v>327500</v>
       </c>
       <c r="F27" s="3">
-        <v>-22800</v>
+        <v>279600</v>
       </c>
       <c r="G27" s="3">
-        <v>64000</v>
+        <v>-22900</v>
       </c>
       <c r="H27" s="3">
-        <v>204000</v>
+        <v>64200</v>
       </c>
       <c r="I27" s="3">
-        <v>-51000</v>
+        <v>204600</v>
       </c>
       <c r="J27" s="3">
+        <v>-51100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-565500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>57600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>112400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>161400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200700</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,30 +1604,33 @@
       <c r="H29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J29" s="3">
         <v>17400</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>4800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-8800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-9400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11900</v>
+        <v>153400</v>
       </c>
       <c r="E32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F32" s="3">
         <v>9800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17400</v>
       </c>
-      <c r="G32" s="3">
-        <v>4300</v>
-      </c>
       <c r="H32" s="3">
-        <v>38000</v>
+        <v>4400</v>
       </c>
       <c r="I32" s="3">
-        <v>10800</v>
+        <v>38100</v>
       </c>
       <c r="J32" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>87300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>70300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>160800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>326600</v>
+        <v>136000</v>
       </c>
       <c r="E33" s="3">
-        <v>278800</v>
+        <v>327500</v>
       </c>
       <c r="F33" s="3">
-        <v>-22800</v>
+        <v>279600</v>
       </c>
       <c r="G33" s="3">
-        <v>64000</v>
+        <v>-22900</v>
       </c>
       <c r="H33" s="3">
-        <v>204000</v>
+        <v>64200</v>
       </c>
       <c r="I33" s="3">
-        <v>-33600</v>
+        <v>204600</v>
       </c>
       <c r="J33" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-565500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>57600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>152600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-210100</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>326600</v>
+        <v>136000</v>
       </c>
       <c r="E35" s="3">
-        <v>278800</v>
+        <v>327500</v>
       </c>
       <c r="F35" s="3">
-        <v>-22800</v>
+        <v>279600</v>
       </c>
       <c r="G35" s="3">
-        <v>64000</v>
+        <v>-22900</v>
       </c>
       <c r="H35" s="3">
-        <v>204000</v>
+        <v>64200</v>
       </c>
       <c r="I35" s="3">
-        <v>-33600</v>
+        <v>204600</v>
       </c>
       <c r="J35" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-565500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>57600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>152600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-210100</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>180100</v>
+        <v>219800</v>
       </c>
       <c r="E41" s="3">
-        <v>159500</v>
+        <v>180600</v>
       </c>
       <c r="F41" s="3">
-        <v>476300</v>
+        <v>160000</v>
       </c>
       <c r="G41" s="3">
-        <v>199600</v>
+        <v>477700</v>
       </c>
       <c r="H41" s="3">
-        <v>177900</v>
+        <v>200200</v>
       </c>
       <c r="I41" s="3">
-        <v>291900</v>
+        <v>178400</v>
       </c>
       <c r="J41" s="3">
+        <v>292700</v>
+      </c>
+      <c r="K41" s="3">
         <v>376500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>481800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>189700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>277500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>153700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>120900</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1973,314 +2062,338 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>927000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>49300</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>576100</v>
+        <v>533200</v>
       </c>
       <c r="E43" s="3">
-        <v>731300</v>
+        <v>577800</v>
       </c>
       <c r="F43" s="3">
-        <v>434000</v>
+        <v>733400</v>
       </c>
       <c r="G43" s="3">
-        <v>505600</v>
+        <v>435200</v>
       </c>
       <c r="H43" s="3">
-        <v>623900</v>
+        <v>507100</v>
       </c>
       <c r="I43" s="3">
-        <v>445900</v>
+        <v>625700</v>
       </c>
       <c r="J43" s="3">
+        <v>447200</v>
+      </c>
+      <c r="K43" s="3">
         <v>375400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>370600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>637900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>574200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1042000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>616300</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1432200</v>
+        <v>1194700</v>
       </c>
       <c r="E44" s="3">
-        <v>1139300</v>
+        <v>1436300</v>
       </c>
       <c r="F44" s="3">
-        <v>631500</v>
+        <v>1142500</v>
       </c>
       <c r="G44" s="3">
-        <v>726900</v>
+        <v>633300</v>
       </c>
       <c r="H44" s="3">
-        <v>716100</v>
+        <v>729000</v>
       </c>
       <c r="I44" s="3">
-        <v>697700</v>
+        <v>718100</v>
       </c>
       <c r="J44" s="3">
+        <v>699600</v>
+      </c>
+      <c r="K44" s="3">
         <v>641200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>553300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>487800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>392400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>422700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>495300</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>42300</v>
+        <v>32600</v>
       </c>
       <c r="E45" s="3">
-        <v>72700</v>
+        <v>42400</v>
       </c>
       <c r="F45" s="3">
-        <v>48800</v>
+        <v>72900</v>
       </c>
       <c r="G45" s="3">
-        <v>32500</v>
+        <v>49000</v>
       </c>
       <c r="H45" s="3">
-        <v>45600</v>
+        <v>32600</v>
       </c>
       <c r="I45" s="3">
-        <v>83500</v>
+        <v>45700</v>
       </c>
       <c r="J45" s="3">
+        <v>83800</v>
+      </c>
+      <c r="K45" s="3">
         <v>136700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>86800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>83600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2230800</v>
+        <v>1980300</v>
       </c>
       <c r="E46" s="3">
-        <v>2102700</v>
+        <v>2237100</v>
       </c>
       <c r="F46" s="3">
-        <v>1590600</v>
+        <v>2108700</v>
       </c>
       <c r="G46" s="3">
-        <v>1464800</v>
+        <v>1595200</v>
       </c>
       <c r="H46" s="3">
-        <v>1563500</v>
+        <v>1468900</v>
       </c>
       <c r="I46" s="3">
-        <v>1519000</v>
+        <v>1568000</v>
       </c>
       <c r="J46" s="3">
+        <v>1523300</v>
+      </c>
+      <c r="K46" s="3">
         <v>1529800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1492400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2325900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1303900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1138600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1293500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>46700</v>
+        <v>33700</v>
       </c>
       <c r="E47" s="3">
-        <v>59700</v>
+        <v>46800</v>
       </c>
       <c r="F47" s="3">
-        <v>73800</v>
+        <v>59800</v>
       </c>
       <c r="G47" s="3">
-        <v>66200</v>
+        <v>74000</v>
       </c>
       <c r="H47" s="3">
-        <v>70500</v>
+        <v>66400</v>
       </c>
       <c r="I47" s="3">
-        <v>53200</v>
+        <v>70700</v>
       </c>
       <c r="J47" s="3">
+        <v>53300</v>
+      </c>
+      <c r="K47" s="3">
         <v>68400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>84700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>81300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>83400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>111500</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2188400</v>
+        <v>2227300</v>
       </c>
       <c r="E48" s="3">
-        <v>2113600</v>
+        <v>2194700</v>
       </c>
       <c r="F48" s="3">
-        <v>2068000</v>
+        <v>2119600</v>
       </c>
       <c r="G48" s="3">
-        <v>2230800</v>
+        <v>2073900</v>
       </c>
       <c r="H48" s="3">
-        <v>1807600</v>
+        <v>2237100</v>
       </c>
       <c r="I48" s="3">
-        <v>1645900</v>
+        <v>1812800</v>
       </c>
       <c r="J48" s="3">
+        <v>1650600</v>
+      </c>
+      <c r="K48" s="3">
         <v>1602500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1281100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>713600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>488000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>663200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>232400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>577200</v>
+        <v>553800</v>
       </c>
       <c r="E49" s="3">
-        <v>552300</v>
+        <v>578900</v>
       </c>
       <c r="F49" s="3">
-        <v>518600</v>
+        <v>553800</v>
       </c>
       <c r="G49" s="3">
-        <v>569600</v>
+        <v>520100</v>
       </c>
       <c r="H49" s="3">
-        <v>533800</v>
+        <v>571300</v>
       </c>
       <c r="I49" s="3">
-        <v>511000</v>
+        <v>535300</v>
       </c>
       <c r="J49" s="3">
+        <v>512500</v>
+      </c>
+      <c r="K49" s="3">
         <v>581600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>531800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>31600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>25100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>317900</v>
+        <v>276400</v>
       </c>
       <c r="E52" s="3">
-        <v>188800</v>
+        <v>318800</v>
       </c>
       <c r="F52" s="3">
-        <v>228900</v>
+        <v>189300</v>
       </c>
       <c r="G52" s="3">
-        <v>208300</v>
+        <v>229600</v>
       </c>
       <c r="H52" s="3">
-        <v>257100</v>
+        <v>208900</v>
       </c>
       <c r="I52" s="3">
-        <v>297300</v>
+        <v>257900</v>
       </c>
       <c r="J52" s="3">
+        <v>298100</v>
+      </c>
+      <c r="K52" s="3">
         <v>326600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>313400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>268700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>211700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>225100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>240600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5361000</v>
+        <v>5071600</v>
       </c>
       <c r="E54" s="3">
-        <v>5017000</v>
+        <v>5376300</v>
       </c>
       <c r="F54" s="3">
-        <v>4480000</v>
+        <v>5031400</v>
       </c>
       <c r="G54" s="3">
-        <v>4539600</v>
+        <v>4492800</v>
       </c>
       <c r="H54" s="3">
-        <v>4232600</v>
+        <v>4552600</v>
       </c>
       <c r="I54" s="3">
-        <v>4026400</v>
+        <v>4244700</v>
       </c>
       <c r="J54" s="3">
+        <v>4037900</v>
+      </c>
+      <c r="K54" s="3">
         <v>4108900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3703500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3400800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2110100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1790800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1892200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1253200</v>
+        <v>1374300</v>
       </c>
       <c r="E57" s="3">
-        <v>1155500</v>
+        <v>1256800</v>
       </c>
       <c r="F57" s="3">
-        <v>679200</v>
+        <v>1158800</v>
       </c>
       <c r="G57" s="3">
-        <v>771400</v>
+        <v>681200</v>
       </c>
       <c r="H57" s="3">
-        <v>743200</v>
+        <v>773600</v>
       </c>
       <c r="I57" s="3">
-        <v>777900</v>
+        <v>745300</v>
       </c>
       <c r="J57" s="3">
+        <v>780200</v>
+      </c>
+      <c r="K57" s="3">
         <v>680300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>670700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>744100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>561000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>965100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>544600</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>160600</v>
+        <v>58800</v>
       </c>
       <c r="E58" s="3">
-        <v>279900</v>
+        <v>161000</v>
       </c>
       <c r="F58" s="3">
-        <v>99800</v>
+        <v>280700</v>
       </c>
       <c r="G58" s="3">
-        <v>218100</v>
+        <v>100100</v>
       </c>
       <c r="H58" s="3">
-        <v>61800</v>
+        <v>218700</v>
       </c>
       <c r="I58" s="3">
-        <v>115000</v>
+        <v>62000</v>
       </c>
       <c r="J58" s="3">
+        <v>115300</v>
+      </c>
+      <c r="K58" s="3">
         <v>116100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>172500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>53100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>85700</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>423100</v>
+        <v>77300</v>
       </c>
       <c r="E59" s="3">
-        <v>424200</v>
+        <v>424400</v>
       </c>
       <c r="F59" s="3">
-        <v>399300</v>
+        <v>425400</v>
       </c>
       <c r="G59" s="3">
-        <v>390600</v>
+        <v>400400</v>
       </c>
       <c r="H59" s="3">
-        <v>430700</v>
+        <v>391700</v>
       </c>
       <c r="I59" s="3">
-        <v>311400</v>
+        <v>432000</v>
       </c>
       <c r="J59" s="3">
+        <v>312300</v>
+      </c>
+      <c r="K59" s="3">
         <v>326600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>387900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>397400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>319400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>269000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>410800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1836900</v>
+        <v>1510300</v>
       </c>
       <c r="E60" s="3">
-        <v>1859700</v>
+        <v>1842200</v>
       </c>
       <c r="F60" s="3">
-        <v>1178300</v>
+        <v>1865000</v>
       </c>
       <c r="G60" s="3">
-        <v>1380100</v>
+        <v>1181700</v>
       </c>
       <c r="H60" s="3">
-        <v>1235800</v>
+        <v>1384100</v>
       </c>
       <c r="I60" s="3">
-        <v>1204300</v>
+        <v>1239300</v>
       </c>
       <c r="J60" s="3">
+        <v>1207800</v>
+      </c>
+      <c r="K60" s="3">
         <v>1123000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1231100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1194600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>906700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>818000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>987200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2070200</v>
+        <v>1973800</v>
       </c>
       <c r="E61" s="3">
-        <v>2030000</v>
+        <v>2076100</v>
       </c>
       <c r="F61" s="3">
-        <v>2494400</v>
+        <v>2035800</v>
       </c>
       <c r="G61" s="3">
-        <v>2343600</v>
+        <v>2501500</v>
       </c>
       <c r="H61" s="3">
-        <v>2272000</v>
+        <v>2350300</v>
       </c>
       <c r="I61" s="3">
-        <v>2192800</v>
+        <v>2278500</v>
       </c>
       <c r="J61" s="3">
+        <v>2199100</v>
+      </c>
+      <c r="K61" s="3">
         <v>2561700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2106900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1360600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>390000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>153700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>165500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>627100</v>
+        <v>647400</v>
       </c>
       <c r="E62" s="3">
-        <v>811600</v>
+        <v>628900</v>
       </c>
       <c r="F62" s="3">
-        <v>916800</v>
+        <v>813900</v>
       </c>
       <c r="G62" s="3">
-        <v>908100</v>
+        <v>919400</v>
       </c>
       <c r="H62" s="3">
-        <v>848500</v>
+        <v>910700</v>
       </c>
       <c r="I62" s="3">
-        <v>975400</v>
+        <v>850900</v>
       </c>
       <c r="J62" s="3">
+        <v>978200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1042700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>916700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>887500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>770400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>859700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1172600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4567800</v>
+        <v>4154400</v>
       </c>
       <c r="E66" s="3">
-        <v>4719800</v>
+        <v>4580900</v>
       </c>
       <c r="F66" s="3">
-        <v>4604700</v>
+        <v>4733200</v>
       </c>
       <c r="G66" s="3">
-        <v>4643800</v>
+        <v>4617900</v>
       </c>
       <c r="H66" s="3">
-        <v>4365000</v>
+        <v>4657100</v>
       </c>
       <c r="I66" s="3">
-        <v>4381200</v>
+        <v>4377400</v>
       </c>
       <c r="J66" s="3">
+        <v>4393700</v>
+      </c>
+      <c r="K66" s="3">
         <v>4737100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4265900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3449400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2071800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1835900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2027200</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>300500</v>
+        <v>457000</v>
       </c>
       <c r="E72" s="3">
-        <v>-177900</v>
+        <v>301400</v>
       </c>
       <c r="F72" s="3">
-        <v>-579400</v>
+        <v>-178400</v>
       </c>
       <c r="G72" s="3">
-        <v>-556600</v>
+        <v>-581000</v>
       </c>
       <c r="H72" s="3">
-        <v>-585900</v>
+        <v>-558200</v>
       </c>
       <c r="I72" s="3">
-        <v>-820300</v>
+        <v>-587600</v>
       </c>
       <c r="J72" s="3">
+        <v>-822600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-799600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-736000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-208900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-141200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-289900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-233600</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>793100</v>
+        <v>917300</v>
       </c>
       <c r="E76" s="3">
-        <v>297300</v>
+        <v>795400</v>
       </c>
       <c r="F76" s="3">
-        <v>-124800</v>
+        <v>298100</v>
       </c>
       <c r="G76" s="3">
-        <v>-104200</v>
+        <v>-125100</v>
       </c>
       <c r="H76" s="3">
-        <v>-132400</v>
+        <v>-104500</v>
       </c>
       <c r="I76" s="3">
-        <v>-354800</v>
+        <v>-132700</v>
       </c>
       <c r="J76" s="3">
+        <v>-355800</v>
+      </c>
+      <c r="K76" s="3">
         <v>-628200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-562500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-48600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-45000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-135000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>326600</v>
+        <v>136000</v>
       </c>
       <c r="E81" s="3">
-        <v>278800</v>
+        <v>327500</v>
       </c>
       <c r="F81" s="3">
-        <v>-22800</v>
+        <v>279600</v>
       </c>
       <c r="G81" s="3">
-        <v>64000</v>
+        <v>-22900</v>
       </c>
       <c r="H81" s="3">
-        <v>204000</v>
+        <v>64200</v>
       </c>
       <c r="I81" s="3">
-        <v>-33600</v>
+        <v>204600</v>
       </c>
       <c r="J81" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-565500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>57600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>152600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-210100</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>311400</v>
+        <v>319900</v>
       </c>
       <c r="E83" s="3">
-        <v>289700</v>
+        <v>312300</v>
       </c>
       <c r="F83" s="3">
-        <v>281000</v>
+        <v>290500</v>
       </c>
       <c r="G83" s="3">
-        <v>277800</v>
+        <v>281800</v>
       </c>
       <c r="H83" s="3">
-        <v>213700</v>
+        <v>278600</v>
       </c>
       <c r="I83" s="3">
-        <v>185500</v>
+        <v>214400</v>
       </c>
       <c r="J83" s="3">
+        <v>186100</v>
+      </c>
+      <c r="K83" s="3">
         <v>168200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>142900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2300</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>488300</v>
+        <v>551700</v>
       </c>
       <c r="E89" s="3">
-        <v>387300</v>
+        <v>489600</v>
       </c>
       <c r="F89" s="3">
-        <v>362400</v>
+        <v>388500</v>
       </c>
       <c r="G89" s="3">
-        <v>485000</v>
+        <v>363400</v>
       </c>
       <c r="H89" s="3">
-        <v>71600</v>
+        <v>486400</v>
       </c>
       <c r="I89" s="3">
-        <v>173600</v>
+        <v>71800</v>
       </c>
       <c r="J89" s="3">
+        <v>174100</v>
+      </c>
+      <c r="K89" s="3">
         <v>95500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>521600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>239400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>220100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>270100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-34000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-296200</v>
+        <v>-366700</v>
       </c>
       <c r="E91" s="3">
-        <v>-251700</v>
+        <v>-297100</v>
       </c>
       <c r="F91" s="3">
-        <v>-197500</v>
+        <v>-252400</v>
       </c>
       <c r="G91" s="3">
-        <v>-294000</v>
+        <v>-198000</v>
       </c>
       <c r="H91" s="3">
-        <v>-300500</v>
+        <v>-294900</v>
       </c>
       <c r="I91" s="3">
-        <v>-299500</v>
+        <v>-301400</v>
       </c>
       <c r="J91" s="3">
+        <v>-300300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-385200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-357300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-224700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-172300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-138300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-113900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-293000</v>
+        <v>-313400</v>
       </c>
       <c r="E94" s="3">
-        <v>-239800</v>
+        <v>-293800</v>
       </c>
       <c r="F94" s="3">
-        <v>-191000</v>
+        <v>-240500</v>
       </c>
       <c r="G94" s="3">
-        <v>-383000</v>
+        <v>-191500</v>
       </c>
       <c r="H94" s="3">
-        <v>-98700</v>
+        <v>-384100</v>
       </c>
       <c r="I94" s="3">
-        <v>-316800</v>
+        <v>-99000</v>
       </c>
       <c r="J94" s="3">
+        <v>-317700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-396000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-737000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-243900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-157900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-143800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-81000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4021,17 +4254,20 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-175800</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-176900</v>
+        <v>-198000</v>
       </c>
       <c r="E100" s="3">
-        <v>-472000</v>
+        <v>-177400</v>
       </c>
       <c r="F100" s="3">
-        <v>109600</v>
+        <v>-473300</v>
       </c>
       <c r="G100" s="3">
-        <v>-82500</v>
+        <v>109900</v>
       </c>
       <c r="H100" s="3">
-        <v>-89000</v>
+        <v>-82700</v>
       </c>
       <c r="I100" s="3">
-        <v>66200</v>
+        <v>-89200</v>
       </c>
       <c r="J100" s="3">
+        <v>66400</v>
+      </c>
+      <c r="K100" s="3">
         <v>157300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-314400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>850200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>51400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-94400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>235900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7600</v>
       </c>
-      <c r="F101" s="3">
-        <v>-4300</v>
-      </c>
       <c r="G101" s="3">
-        <v>2200</v>
+        <v>-4400</v>
       </c>
       <c r="H101" s="3">
         <v>2200</v>
       </c>
       <c r="I101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J101" s="3">
         <v>-7600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>11700</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>20600</v>
+        <v>40300</v>
       </c>
       <c r="E102" s="3">
-        <v>-316800</v>
+        <v>20700</v>
       </c>
       <c r="F102" s="3">
-        <v>276700</v>
+        <v>-317700</v>
       </c>
       <c r="G102" s="3">
-        <v>21700</v>
+        <v>277500</v>
       </c>
       <c r="H102" s="3">
-        <v>-113900</v>
+        <v>21800</v>
       </c>
       <c r="I102" s="3">
-        <v>-84600</v>
+        <v>-114300</v>
       </c>
       <c r="J102" s="3">
+        <v>-84900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-140000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-525700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>852500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>112400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>132600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>CSTM</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7876800</v>
+        <v>7823200</v>
       </c>
       <c r="E8" s="3">
-        <v>8835400</v>
+        <v>8775300</v>
       </c>
       <c r="F8" s="3">
-        <v>6694000</v>
+        <v>6648500</v>
       </c>
       <c r="G8" s="3">
-        <v>5313200</v>
+        <v>5277100</v>
       </c>
       <c r="H8" s="3">
-        <v>6427400</v>
+        <v>6383700</v>
       </c>
       <c r="I8" s="3">
-        <v>6186900</v>
+        <v>6144900</v>
       </c>
       <c r="J8" s="3">
-        <v>5698400</v>
+        <v>5659600</v>
       </c>
       <c r="K8" s="3">
         <v>5146200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7104200</v>
+        <v>7055900</v>
       </c>
       <c r="E9" s="3">
-        <v>8104200</v>
+        <v>8049100</v>
       </c>
       <c r="F9" s="3">
-        <v>5971500</v>
+        <v>5930900</v>
       </c>
       <c r="G9" s="3">
-        <v>4780000</v>
+        <v>4747500</v>
       </c>
       <c r="H9" s="3">
-        <v>5772400</v>
+        <v>5733100</v>
       </c>
       <c r="I9" s="3">
-        <v>5601500</v>
+        <v>5563400</v>
       </c>
       <c r="J9" s="3">
-        <v>5111900</v>
+        <v>5077100</v>
       </c>
       <c r="K9" s="3">
         <v>4586300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>772600</v>
+        <v>767300</v>
       </c>
       <c r="E10" s="3">
-        <v>731200</v>
+        <v>726200</v>
       </c>
       <c r="F10" s="3">
-        <v>722500</v>
+        <v>717600</v>
       </c>
       <c r="G10" s="3">
-        <v>533200</v>
+        <v>529500</v>
       </c>
       <c r="H10" s="3">
-        <v>655000</v>
+        <v>650600</v>
       </c>
       <c r="I10" s="3">
-        <v>585400</v>
+        <v>581400</v>
       </c>
       <c r="J10" s="3">
-        <v>586500</v>
+        <v>582500</v>
       </c>
       <c r="K10" s="3">
         <v>559900</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>56600</v>
+        <v>50800</v>
       </c>
       <c r="E12" s="3">
-        <v>46800</v>
+        <v>46500</v>
       </c>
       <c r="F12" s="3">
-        <v>37000</v>
+        <v>36700</v>
       </c>
       <c r="G12" s="3">
-        <v>37000</v>
+        <v>36700</v>
       </c>
       <c r="H12" s="3">
-        <v>45700</v>
+        <v>45400</v>
       </c>
       <c r="I12" s="3">
-        <v>39200</v>
+        <v>38900</v>
       </c>
       <c r="J12" s="3">
-        <v>35900</v>
+        <v>35700</v>
       </c>
       <c r="K12" s="3">
         <v>34700</v>
@@ -969,26 +969,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>11</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>-50100</v>
+        <v>-49700</v>
       </c>
       <c r="F14" s="3">
-        <v>67500</v>
+        <v>67000</v>
       </c>
       <c r="G14" s="3">
-        <v>69600</v>
+        <v>69200</v>
       </c>
       <c r="H14" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="I14" s="3">
-        <v>-38100</v>
+        <v>-37800</v>
       </c>
       <c r="J14" s="3">
-        <v>81600</v>
+        <v>81100</v>
       </c>
       <c r="K14" s="3">
         <v>5400</v>
@@ -1014,26 +1014,26 @@
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>11</v>
+      <c r="D15" s="3">
+        <v>18400</v>
       </c>
       <c r="E15" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="F15" s="3">
-        <v>23900</v>
+        <v>23800</v>
       </c>
       <c r="G15" s="3">
-        <v>20700</v>
+        <v>20500</v>
       </c>
       <c r="H15" s="3">
-        <v>20700</v>
+        <v>20500</v>
       </c>
       <c r="I15" s="3">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="J15" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="K15" s="3">
         <v>8700</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7510100</v>
+        <v>7459000</v>
       </c>
       <c r="E17" s="3">
-        <v>8471900</v>
+        <v>8414300</v>
       </c>
       <c r="F17" s="3">
-        <v>6196700</v>
+        <v>6154600</v>
       </c>
       <c r="G17" s="3">
-        <v>5177200</v>
+        <v>5142000</v>
       </c>
       <c r="H17" s="3">
-        <v>6149900</v>
+        <v>6108100</v>
       </c>
       <c r="I17" s="3">
-        <v>5747300</v>
+        <v>5708300</v>
       </c>
       <c r="J17" s="3">
-        <v>5448100</v>
+        <v>5411100</v>
       </c>
       <c r="K17" s="3">
         <v>4879200</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>366700</v>
+        <v>364200</v>
       </c>
       <c r="E18" s="3">
-        <v>363400</v>
+        <v>361000</v>
       </c>
       <c r="F18" s="3">
-        <v>497300</v>
+        <v>493900</v>
       </c>
       <c r="G18" s="3">
-        <v>136000</v>
+        <v>135100</v>
       </c>
       <c r="H18" s="3">
-        <v>277500</v>
+        <v>275600</v>
       </c>
       <c r="I18" s="3">
-        <v>439600</v>
+        <v>436600</v>
       </c>
       <c r="J18" s="3">
-        <v>250300</v>
+        <v>248600</v>
       </c>
       <c r="K18" s="3">
         <v>266900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-153400</v>
+        <v>-16200</v>
       </c>
       <c r="E20" s="3">
-        <v>-12000</v>
+        <v>-11900</v>
       </c>
       <c r="F20" s="3">
-        <v>-9800</v>
+        <v>-9700</v>
       </c>
       <c r="G20" s="3">
-        <v>-17400</v>
+        <v>-17300</v>
       </c>
       <c r="H20" s="3">
-        <v>-4400</v>
+        <v>-4300</v>
       </c>
       <c r="I20" s="3">
-        <v>-38100</v>
+        <v>-37800</v>
       </c>
       <c r="J20" s="3">
-        <v>-10900</v>
+        <v>-10800</v>
       </c>
       <c r="K20" s="3">
         <v>3300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>535100</v>
+        <v>663700</v>
       </c>
       <c r="E21" s="3">
-        <v>665600</v>
+        <v>657300</v>
       </c>
       <c r="F21" s="3">
-        <v>779700</v>
+        <v>770900</v>
       </c>
       <c r="G21" s="3">
-        <v>402100</v>
+        <v>395900</v>
       </c>
       <c r="H21" s="3">
-        <v>553300</v>
+        <v>546200</v>
       </c>
       <c r="I21" s="3">
-        <v>617100</v>
+        <v>610300</v>
       </c>
       <c r="J21" s="3">
-        <v>426600</v>
+        <v>421400</v>
       </c>
       <c r="K21" s="3">
         <v>438300</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>11</v>
+      <c r="D22" s="3">
+        <v>136200</v>
       </c>
       <c r="E22" s="3">
-        <v>130600</v>
+        <v>129700</v>
       </c>
       <c r="F22" s="3">
-        <v>142500</v>
+        <v>141600</v>
       </c>
       <c r="G22" s="3">
-        <v>155600</v>
+        <v>154500</v>
       </c>
       <c r="H22" s="3">
-        <v>183900</v>
+        <v>182600</v>
       </c>
       <c r="I22" s="3">
-        <v>160000</v>
+        <v>158900</v>
       </c>
       <c r="J22" s="3">
-        <v>186100</v>
+        <v>184800</v>
       </c>
       <c r="K22" s="3">
         <v>199600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>213300</v>
+        <v>211800</v>
       </c>
       <c r="E23" s="3">
-        <v>220900</v>
+        <v>219400</v>
       </c>
       <c r="F23" s="3">
-        <v>344900</v>
+        <v>342600</v>
       </c>
       <c r="G23" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="H23" s="3">
-        <v>89200</v>
+        <v>88600</v>
       </c>
       <c r="I23" s="3">
-        <v>241600</v>
+        <v>239900</v>
       </c>
       <c r="J23" s="3">
-        <v>53300</v>
+        <v>53000</v>
       </c>
       <c r="K23" s="3">
         <v>70500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>72900</v>
+        <v>72400</v>
       </c>
       <c r="E24" s="3">
-        <v>-114300</v>
+        <v>-113500</v>
       </c>
       <c r="F24" s="3">
-        <v>59800</v>
+        <v>59400</v>
       </c>
       <c r="G24" s="3">
-        <v>-18500</v>
+        <v>-18400</v>
       </c>
       <c r="H24" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="I24" s="3">
-        <v>34800</v>
+        <v>34600</v>
       </c>
       <c r="J24" s="3">
-        <v>104500</v>
+        <v>103700</v>
       </c>
       <c r="K24" s="3">
         <v>74900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>140400</v>
+        <v>139400</v>
       </c>
       <c r="E26" s="3">
-        <v>335100</v>
+        <v>332900</v>
       </c>
       <c r="F26" s="3">
-        <v>285100</v>
+        <v>283100</v>
       </c>
       <c r="G26" s="3">
-        <v>-18500</v>
+        <v>-18400</v>
       </c>
       <c r="H26" s="3">
-        <v>69600</v>
+        <v>69200</v>
       </c>
       <c r="I26" s="3">
-        <v>206700</v>
+        <v>205300</v>
       </c>
       <c r="J26" s="3">
-        <v>-51100</v>
+        <v>-50800</v>
       </c>
       <c r="K26" s="3">
         <v>-4300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>136000</v>
+        <v>135100</v>
       </c>
       <c r="E27" s="3">
-        <v>327500</v>
+        <v>325300</v>
       </c>
       <c r="F27" s="3">
-        <v>279600</v>
+        <v>277700</v>
       </c>
       <c r="G27" s="3">
-        <v>-22900</v>
+        <v>-22700</v>
       </c>
       <c r="H27" s="3">
-        <v>64200</v>
+        <v>63800</v>
       </c>
       <c r="I27" s="3">
-        <v>204600</v>
+        <v>203200</v>
       </c>
       <c r="J27" s="3">
-        <v>-51100</v>
+        <v>-50800</v>
       </c>
       <c r="K27" s="3">
         <v>-4300</v>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="3">
-        <v>17400</v>
+        <v>17300</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>11</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>153400</v>
+        <v>16200</v>
       </c>
       <c r="E32" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="F32" s="3">
-        <v>9800</v>
+        <v>9700</v>
       </c>
       <c r="G32" s="3">
-        <v>17400</v>
+        <v>17300</v>
       </c>
       <c r="H32" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="I32" s="3">
-        <v>38100</v>
+        <v>37800</v>
       </c>
       <c r="J32" s="3">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="K32" s="3">
         <v>-3300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>136000</v>
+        <v>135100</v>
       </c>
       <c r="E33" s="3">
-        <v>327500</v>
+        <v>325300</v>
       </c>
       <c r="F33" s="3">
-        <v>279600</v>
+        <v>277700</v>
       </c>
       <c r="G33" s="3">
-        <v>-22900</v>
+        <v>-22700</v>
       </c>
       <c r="H33" s="3">
-        <v>64200</v>
+        <v>63800</v>
       </c>
       <c r="I33" s="3">
-        <v>204600</v>
+        <v>203200</v>
       </c>
       <c r="J33" s="3">
-        <v>-33700</v>
+        <v>-33500</v>
       </c>
       <c r="K33" s="3">
         <v>-4300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>136000</v>
+        <v>135100</v>
       </c>
       <c r="E35" s="3">
-        <v>327500</v>
+        <v>325300</v>
       </c>
       <c r="F35" s="3">
-        <v>279600</v>
+        <v>277700</v>
       </c>
       <c r="G35" s="3">
-        <v>-22900</v>
+        <v>-22700</v>
       </c>
       <c r="H35" s="3">
-        <v>64200</v>
+        <v>63800</v>
       </c>
       <c r="I35" s="3">
-        <v>204600</v>
+        <v>203200</v>
       </c>
       <c r="J35" s="3">
-        <v>-33700</v>
+        <v>-33500</v>
       </c>
       <c r="K35" s="3">
         <v>-4300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>219800</v>
+        <v>218300</v>
       </c>
       <c r="E41" s="3">
-        <v>180600</v>
+        <v>179400</v>
       </c>
       <c r="F41" s="3">
-        <v>160000</v>
+        <v>158900</v>
       </c>
       <c r="G41" s="3">
-        <v>477700</v>
+        <v>474400</v>
       </c>
       <c r="H41" s="3">
-        <v>200200</v>
+        <v>198800</v>
       </c>
       <c r="I41" s="3">
-        <v>178400</v>
+        <v>177200</v>
       </c>
       <c r="J41" s="3">
-        <v>292700</v>
+        <v>290700</v>
       </c>
       <c r="K41" s="3">
         <v>376500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>533200</v>
+        <v>520900</v>
       </c>
       <c r="E43" s="3">
-        <v>577800</v>
+        <v>573900</v>
       </c>
       <c r="F43" s="3">
-        <v>733400</v>
+        <v>728400</v>
       </c>
       <c r="G43" s="3">
-        <v>435200</v>
+        <v>432300</v>
       </c>
       <c r="H43" s="3">
-        <v>507100</v>
+        <v>503600</v>
       </c>
       <c r="I43" s="3">
-        <v>625700</v>
+        <v>621400</v>
       </c>
       <c r="J43" s="3">
-        <v>447200</v>
+        <v>444200</v>
       </c>
       <c r="K43" s="3">
         <v>375400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1194700</v>
+        <v>1186600</v>
       </c>
       <c r="E44" s="3">
-        <v>1436300</v>
+        <v>1426500</v>
       </c>
       <c r="F44" s="3">
-        <v>1142500</v>
+        <v>1134700</v>
       </c>
       <c r="G44" s="3">
-        <v>633300</v>
+        <v>629000</v>
       </c>
       <c r="H44" s="3">
-        <v>729000</v>
+        <v>724100</v>
       </c>
       <c r="I44" s="3">
-        <v>718100</v>
+        <v>713300</v>
       </c>
       <c r="J44" s="3">
-        <v>699600</v>
+        <v>694900</v>
       </c>
       <c r="K44" s="3">
         <v>641200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32600</v>
+        <v>41100</v>
       </c>
       <c r="E45" s="3">
-        <v>42400</v>
+        <v>42100</v>
       </c>
       <c r="F45" s="3">
-        <v>72900</v>
+        <v>72400</v>
       </c>
       <c r="G45" s="3">
-        <v>49000</v>
+        <v>48600</v>
       </c>
       <c r="H45" s="3">
-        <v>32600</v>
+        <v>32400</v>
       </c>
       <c r="I45" s="3">
-        <v>45700</v>
+        <v>45400</v>
       </c>
       <c r="J45" s="3">
-        <v>83800</v>
+        <v>83200</v>
       </c>
       <c r="K45" s="3">
         <v>136700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1980300</v>
+        <v>1966900</v>
       </c>
       <c r="E46" s="3">
-        <v>2237100</v>
+        <v>2221900</v>
       </c>
       <c r="F46" s="3">
-        <v>2108700</v>
+        <v>2094400</v>
       </c>
       <c r="G46" s="3">
-        <v>1595200</v>
+        <v>1584300</v>
       </c>
       <c r="H46" s="3">
-        <v>1468900</v>
+        <v>1458900</v>
       </c>
       <c r="I46" s="3">
-        <v>1568000</v>
+        <v>1557300</v>
       </c>
       <c r="J46" s="3">
-        <v>1523300</v>
+        <v>1513000</v>
       </c>
       <c r="K46" s="3">
         <v>1529800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>33700</v>
+        <v>33500</v>
       </c>
       <c r="E47" s="3">
-        <v>46800</v>
+        <v>46500</v>
       </c>
       <c r="F47" s="3">
-        <v>59800</v>
+        <v>59400</v>
       </c>
       <c r="G47" s="3">
-        <v>74000</v>
+        <v>73500</v>
       </c>
       <c r="H47" s="3">
-        <v>66400</v>
+        <v>65900</v>
       </c>
       <c r="I47" s="3">
-        <v>70700</v>
+        <v>70200</v>
       </c>
       <c r="J47" s="3">
-        <v>53300</v>
+        <v>53000</v>
       </c>
       <c r="K47" s="3">
         <v>68400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2227300</v>
+        <v>2212200</v>
       </c>
       <c r="E48" s="3">
-        <v>2194700</v>
+        <v>2179800</v>
       </c>
       <c r="F48" s="3">
-        <v>2119600</v>
+        <v>2105200</v>
       </c>
       <c r="G48" s="3">
-        <v>2073900</v>
+        <v>2059800</v>
       </c>
       <c r="H48" s="3">
-        <v>2237100</v>
+        <v>2221900</v>
       </c>
       <c r="I48" s="3">
-        <v>1812800</v>
+        <v>1800400</v>
       </c>
       <c r="J48" s="3">
-        <v>1650600</v>
+        <v>1639400</v>
       </c>
       <c r="K48" s="3">
         <v>1602500</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>553800</v>
+        <v>550100</v>
       </c>
       <c r="E49" s="3">
-        <v>578900</v>
+        <v>574900</v>
       </c>
       <c r="F49" s="3">
-        <v>553800</v>
+        <v>550100</v>
       </c>
       <c r="G49" s="3">
-        <v>520100</v>
+        <v>516600</v>
       </c>
       <c r="H49" s="3">
-        <v>571300</v>
+        <v>567400</v>
       </c>
       <c r="I49" s="3">
-        <v>535300</v>
+        <v>531700</v>
       </c>
       <c r="J49" s="3">
-        <v>512500</v>
+        <v>509000</v>
       </c>
       <c r="K49" s="3">
         <v>581600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>276400</v>
+        <v>274500</v>
       </c>
       <c r="E52" s="3">
-        <v>318800</v>
+        <v>316600</v>
       </c>
       <c r="F52" s="3">
-        <v>189300</v>
+        <v>188000</v>
       </c>
       <c r="G52" s="3">
-        <v>229600</v>
+        <v>228000</v>
       </c>
       <c r="H52" s="3">
-        <v>208900</v>
+        <v>207500</v>
       </c>
       <c r="I52" s="3">
-        <v>257900</v>
+        <v>256100</v>
       </c>
       <c r="J52" s="3">
-        <v>298100</v>
+        <v>296100</v>
       </c>
       <c r="K52" s="3">
         <v>326600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5071600</v>
+        <v>5037100</v>
       </c>
       <c r="E54" s="3">
-        <v>5376300</v>
+        <v>5339700</v>
       </c>
       <c r="F54" s="3">
-        <v>5031400</v>
+        <v>4997200</v>
       </c>
       <c r="G54" s="3">
-        <v>4492800</v>
+        <v>4462200</v>
       </c>
       <c r="H54" s="3">
-        <v>4552600</v>
+        <v>4521600</v>
       </c>
       <c r="I54" s="3">
-        <v>4244700</v>
+        <v>4215800</v>
       </c>
       <c r="J54" s="3">
-        <v>4037900</v>
+        <v>4010500</v>
       </c>
       <c r="K54" s="3">
         <v>4108900</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1374300</v>
+        <v>1006100</v>
       </c>
       <c r="E57" s="3">
-        <v>1256800</v>
+        <v>1248200</v>
       </c>
       <c r="F57" s="3">
-        <v>1158800</v>
+        <v>1150900</v>
       </c>
       <c r="G57" s="3">
-        <v>681200</v>
+        <v>676500</v>
       </c>
       <c r="H57" s="3">
-        <v>773600</v>
+        <v>768400</v>
       </c>
       <c r="I57" s="3">
-        <v>745300</v>
+        <v>740300</v>
       </c>
       <c r="J57" s="3">
-        <v>780200</v>
+        <v>774900</v>
       </c>
       <c r="K57" s="3">
         <v>680300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>58800</v>
+        <v>58400</v>
       </c>
       <c r="E58" s="3">
-        <v>161000</v>
+        <v>159900</v>
       </c>
       <c r="F58" s="3">
-        <v>280700</v>
+        <v>278800</v>
       </c>
       <c r="G58" s="3">
-        <v>100100</v>
+        <v>99400</v>
       </c>
       <c r="H58" s="3">
-        <v>218700</v>
+        <v>217200</v>
       </c>
       <c r="I58" s="3">
-        <v>62000</v>
+        <v>61600</v>
       </c>
       <c r="J58" s="3">
-        <v>115300</v>
+        <v>114600</v>
       </c>
       <c r="K58" s="3">
         <v>116100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>77300</v>
+        <v>435500</v>
       </c>
       <c r="E59" s="3">
-        <v>424400</v>
+        <v>421500</v>
       </c>
       <c r="F59" s="3">
-        <v>425400</v>
+        <v>422600</v>
       </c>
       <c r="G59" s="3">
-        <v>400400</v>
+        <v>397700</v>
       </c>
       <c r="H59" s="3">
-        <v>391700</v>
+        <v>389100</v>
       </c>
       <c r="I59" s="3">
-        <v>432000</v>
+        <v>429000</v>
       </c>
       <c r="J59" s="3">
-        <v>312300</v>
+        <v>310200</v>
       </c>
       <c r="K59" s="3">
         <v>326600</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1510300</v>
+        <v>1500000</v>
       </c>
       <c r="E60" s="3">
-        <v>1842200</v>
+        <v>1829600</v>
       </c>
       <c r="F60" s="3">
-        <v>1865000</v>
+        <v>1852300</v>
       </c>
       <c r="G60" s="3">
-        <v>1181700</v>
+        <v>1173600</v>
       </c>
       <c r="H60" s="3">
-        <v>1384100</v>
+        <v>1374700</v>
       </c>
       <c r="I60" s="3">
-        <v>1239300</v>
+        <v>1230900</v>
       </c>
       <c r="J60" s="3">
-        <v>1207800</v>
+        <v>1199600</v>
       </c>
       <c r="K60" s="3">
         <v>1123000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1973800</v>
+        <v>1960400</v>
       </c>
       <c r="E61" s="3">
-        <v>2076100</v>
+        <v>2062000</v>
       </c>
       <c r="F61" s="3">
-        <v>2035800</v>
+        <v>2022000</v>
       </c>
       <c r="G61" s="3">
-        <v>2501500</v>
+        <v>2484500</v>
       </c>
       <c r="H61" s="3">
-        <v>2350300</v>
+        <v>2334300</v>
       </c>
       <c r="I61" s="3">
-        <v>2278500</v>
+        <v>2263000</v>
       </c>
       <c r="J61" s="3">
-        <v>2199100</v>
+        <v>2184100</v>
       </c>
       <c r="K61" s="3">
         <v>2561700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>647400</v>
+        <v>643000</v>
       </c>
       <c r="E62" s="3">
-        <v>628900</v>
+        <v>624600</v>
       </c>
       <c r="F62" s="3">
-        <v>813900</v>
+        <v>808400</v>
       </c>
       <c r="G62" s="3">
-        <v>919400</v>
+        <v>913200</v>
       </c>
       <c r="H62" s="3">
-        <v>910700</v>
+        <v>904500</v>
       </c>
       <c r="I62" s="3">
-        <v>850900</v>
+        <v>845100</v>
       </c>
       <c r="J62" s="3">
-        <v>978200</v>
+        <v>971500</v>
       </c>
       <c r="K62" s="3">
         <v>1042700</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4154400</v>
+        <v>4126100</v>
       </c>
       <c r="E66" s="3">
-        <v>4580900</v>
+        <v>4549700</v>
       </c>
       <c r="F66" s="3">
-        <v>4733200</v>
+        <v>4701000</v>
       </c>
       <c r="G66" s="3">
-        <v>4617900</v>
+        <v>4586500</v>
       </c>
       <c r="H66" s="3">
-        <v>4657100</v>
+        <v>4625400</v>
       </c>
       <c r="I66" s="3">
-        <v>4377400</v>
+        <v>4347700</v>
       </c>
       <c r="J66" s="3">
-        <v>4393700</v>
+        <v>4363900</v>
       </c>
       <c r="K66" s="3">
         <v>4737100</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>457000</v>
+        <v>440900</v>
       </c>
       <c r="E72" s="3">
-        <v>301400</v>
+        <v>299400</v>
       </c>
       <c r="F72" s="3">
-        <v>-178400</v>
+        <v>-177200</v>
       </c>
       <c r="G72" s="3">
-        <v>-581000</v>
+        <v>-577100</v>
       </c>
       <c r="H72" s="3">
-        <v>-558200</v>
+        <v>-554400</v>
       </c>
       <c r="I72" s="3">
-        <v>-587600</v>
+        <v>-583600</v>
       </c>
       <c r="J72" s="3">
-        <v>-822600</v>
+        <v>-817000</v>
       </c>
       <c r="K72" s="3">
         <v>-799600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>917300</v>
+        <v>911000</v>
       </c>
       <c r="E76" s="3">
-        <v>795400</v>
+        <v>790000</v>
       </c>
       <c r="F76" s="3">
-        <v>298100</v>
+        <v>296100</v>
       </c>
       <c r="G76" s="3">
-        <v>-125100</v>
+        <v>-124300</v>
       </c>
       <c r="H76" s="3">
-        <v>-104500</v>
+        <v>-103700</v>
       </c>
       <c r="I76" s="3">
-        <v>-132700</v>
+        <v>-131800</v>
       </c>
       <c r="J76" s="3">
-        <v>-355800</v>
+        <v>-353400</v>
       </c>
       <c r="K76" s="3">
         <v>-628200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>136000</v>
+        <v>135100</v>
       </c>
       <c r="E81" s="3">
-        <v>327500</v>
+        <v>325300</v>
       </c>
       <c r="F81" s="3">
-        <v>279600</v>
+        <v>277700</v>
       </c>
       <c r="G81" s="3">
-        <v>-22900</v>
+        <v>-22700</v>
       </c>
       <c r="H81" s="3">
-        <v>64200</v>
+        <v>63800</v>
       </c>
       <c r="I81" s="3">
-        <v>204600</v>
+        <v>203200</v>
       </c>
       <c r="J81" s="3">
-        <v>-33700</v>
+        <v>-33500</v>
       </c>
       <c r="K81" s="3">
         <v>-4300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>319900</v>
+        <v>317700</v>
       </c>
       <c r="E83" s="3">
-        <v>312300</v>
+        <v>310200</v>
       </c>
       <c r="F83" s="3">
-        <v>290500</v>
+        <v>288500</v>
       </c>
       <c r="G83" s="3">
-        <v>281800</v>
+        <v>279900</v>
       </c>
       <c r="H83" s="3">
-        <v>278600</v>
+        <v>276700</v>
       </c>
       <c r="I83" s="3">
-        <v>214400</v>
+        <v>212900</v>
       </c>
       <c r="J83" s="3">
-        <v>186100</v>
+        <v>184800</v>
       </c>
       <c r="K83" s="3">
         <v>168200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>551700</v>
+        <v>546800</v>
       </c>
       <c r="E89" s="3">
-        <v>489600</v>
+        <v>486300</v>
       </c>
       <c r="F89" s="3">
-        <v>388500</v>
+        <v>385800</v>
       </c>
       <c r="G89" s="3">
-        <v>363400</v>
+        <v>361000</v>
       </c>
       <c r="H89" s="3">
-        <v>486400</v>
+        <v>483100</v>
       </c>
       <c r="I89" s="3">
-        <v>71800</v>
+        <v>71300</v>
       </c>
       <c r="J89" s="3">
-        <v>174100</v>
+        <v>172900</v>
       </c>
       <c r="K89" s="3">
         <v>95500</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-366700</v>
+        <v>-364200</v>
       </c>
       <c r="E91" s="3">
-        <v>-297100</v>
+        <v>-295000</v>
       </c>
       <c r="F91" s="3">
-        <v>-252400</v>
+        <v>-250700</v>
       </c>
       <c r="G91" s="3">
-        <v>-198000</v>
+        <v>-196700</v>
       </c>
       <c r="H91" s="3">
-        <v>-294900</v>
+        <v>-292900</v>
       </c>
       <c r="I91" s="3">
-        <v>-301400</v>
+        <v>-299400</v>
       </c>
       <c r="J91" s="3">
-        <v>-300300</v>
+        <v>-298300</v>
       </c>
       <c r="K91" s="3">
         <v>-385200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-313400</v>
+        <v>-311200</v>
       </c>
       <c r="E94" s="3">
-        <v>-293800</v>
+        <v>-291800</v>
       </c>
       <c r="F94" s="3">
-        <v>-240500</v>
+        <v>-238800</v>
       </c>
       <c r="G94" s="3">
-        <v>-191500</v>
+        <v>-190200</v>
       </c>
       <c r="H94" s="3">
-        <v>-384100</v>
+        <v>-381500</v>
       </c>
       <c r="I94" s="3">
-        <v>-99000</v>
+        <v>-98300</v>
       </c>
       <c r="J94" s="3">
-        <v>-317700</v>
+        <v>-315600</v>
       </c>
       <c r="K94" s="3">
         <v>-396000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-198000</v>
+        <v>-196700</v>
       </c>
       <c r="E100" s="3">
-        <v>-177400</v>
+        <v>-176200</v>
       </c>
       <c r="F100" s="3">
-        <v>-473300</v>
+        <v>-470100</v>
       </c>
       <c r="G100" s="3">
-        <v>109900</v>
+        <v>109200</v>
       </c>
       <c r="H100" s="3">
-        <v>-82700</v>
+        <v>-82100</v>
       </c>
       <c r="I100" s="3">
-        <v>-89200</v>
+        <v>-88600</v>
       </c>
       <c r="J100" s="3">
-        <v>66400</v>
+        <v>65900</v>
       </c>
       <c r="K100" s="3">
         <v>157300</v>
@@ -4461,7 +4461,7 @@
         <v>7600</v>
       </c>
       <c r="G101" s="3">
-        <v>-4400</v>
+        <v>-4300</v>
       </c>
       <c r="H101" s="3">
         <v>2200</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>40300</v>
+        <v>37800</v>
       </c>
       <c r="E102" s="3">
-        <v>20700</v>
+        <v>20500</v>
       </c>
       <c r="F102" s="3">
-        <v>-317700</v>
+        <v>-315600</v>
       </c>
       <c r="G102" s="3">
-        <v>277500</v>
+        <v>275600</v>
       </c>
       <c r="H102" s="3">
-        <v>21800</v>
+        <v>21600</v>
       </c>
       <c r="I102" s="3">
-        <v>-114300</v>
+        <v>-113500</v>
       </c>
       <c r="J102" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="K102" s="3">
         <v>-140000</v>

--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7823200</v>
+        <v>8017900</v>
       </c>
       <c r="E8" s="3">
-        <v>8775300</v>
+        <v>8993700</v>
       </c>
       <c r="F8" s="3">
-        <v>6648500</v>
+        <v>6814000</v>
       </c>
       <c r="G8" s="3">
-        <v>5277100</v>
+        <v>5408400</v>
       </c>
       <c r="H8" s="3">
-        <v>6383700</v>
+        <v>6542600</v>
       </c>
       <c r="I8" s="3">
-        <v>6144900</v>
+        <v>6297800</v>
       </c>
       <c r="J8" s="3">
-        <v>5659600</v>
+        <v>5800500</v>
       </c>
       <c r="K8" s="3">
         <v>5146200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7055900</v>
+        <v>7231500</v>
       </c>
       <c r="E9" s="3">
-        <v>8049100</v>
+        <v>8249400</v>
       </c>
       <c r="F9" s="3">
-        <v>5930900</v>
+        <v>6078500</v>
       </c>
       <c r="G9" s="3">
-        <v>4747500</v>
+        <v>4865700</v>
       </c>
       <c r="H9" s="3">
-        <v>5733100</v>
+        <v>5875800</v>
       </c>
       <c r="I9" s="3">
-        <v>5563400</v>
+        <v>5701900</v>
       </c>
       <c r="J9" s="3">
-        <v>5077100</v>
+        <v>5203500</v>
       </c>
       <c r="K9" s="3">
         <v>4586300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>767300</v>
+        <v>786400</v>
       </c>
       <c r="E10" s="3">
-        <v>726200</v>
+        <v>744300</v>
       </c>
       <c r="F10" s="3">
-        <v>717600</v>
+        <v>735400</v>
       </c>
       <c r="G10" s="3">
-        <v>529500</v>
+        <v>542700</v>
       </c>
       <c r="H10" s="3">
-        <v>650600</v>
+        <v>666800</v>
       </c>
       <c r="I10" s="3">
-        <v>581400</v>
+        <v>595900</v>
       </c>
       <c r="J10" s="3">
-        <v>582500</v>
+        <v>597000</v>
       </c>
       <c r="K10" s="3">
         <v>559900</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>50800</v>
+        <v>52100</v>
       </c>
       <c r="E12" s="3">
+        <v>47600</v>
+      </c>
+      <c r="F12" s="3">
+        <v>37700</v>
+      </c>
+      <c r="G12" s="3">
+        <v>37700</v>
+      </c>
+      <c r="H12" s="3">
         <v>46500</v>
       </c>
-      <c r="F12" s="3">
-        <v>36700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>36700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>45400</v>
-      </c>
       <c r="I12" s="3">
-        <v>38900</v>
+        <v>39900</v>
       </c>
       <c r="J12" s="3">
-        <v>35700</v>
+        <v>36600</v>
       </c>
       <c r="K12" s="3">
         <v>34700</v>
@@ -973,22 +973,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>-49700</v>
+        <v>-50900</v>
       </c>
       <c r="F14" s="3">
-        <v>67000</v>
+        <v>68700</v>
       </c>
       <c r="G14" s="3">
-        <v>69200</v>
+        <v>70900</v>
       </c>
       <c r="H14" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="I14" s="3">
-        <v>-37800</v>
+        <v>-38800</v>
       </c>
       <c r="J14" s="3">
-        <v>81100</v>
+        <v>83100</v>
       </c>
       <c r="K14" s="3">
         <v>5400</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>18400</v>
+        <v>18800</v>
       </c>
       <c r="E15" s="3">
-        <v>18400</v>
+        <v>18800</v>
       </c>
       <c r="F15" s="3">
-        <v>23800</v>
+        <v>24400</v>
       </c>
       <c r="G15" s="3">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="H15" s="3">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="I15" s="3">
-        <v>14000</v>
+        <v>14400</v>
       </c>
       <c r="J15" s="3">
-        <v>11900</v>
+        <v>12200</v>
       </c>
       <c r="K15" s="3">
         <v>8700</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7459000</v>
+        <v>7644700</v>
       </c>
       <c r="E17" s="3">
-        <v>8414300</v>
+        <v>8623800</v>
       </c>
       <c r="F17" s="3">
-        <v>6154600</v>
+        <v>6307800</v>
       </c>
       <c r="G17" s="3">
-        <v>5142000</v>
+        <v>5270000</v>
       </c>
       <c r="H17" s="3">
-        <v>6108100</v>
+        <v>6260200</v>
       </c>
       <c r="I17" s="3">
-        <v>5708300</v>
+        <v>5850300</v>
       </c>
       <c r="J17" s="3">
-        <v>5411100</v>
+        <v>5545800</v>
       </c>
       <c r="K17" s="3">
         <v>4879200</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>364200</v>
+        <v>373300</v>
       </c>
       <c r="E18" s="3">
-        <v>361000</v>
+        <v>369900</v>
       </c>
       <c r="F18" s="3">
-        <v>493900</v>
+        <v>506200</v>
       </c>
       <c r="G18" s="3">
-        <v>135100</v>
+        <v>138500</v>
       </c>
       <c r="H18" s="3">
-        <v>275600</v>
+        <v>282400</v>
       </c>
       <c r="I18" s="3">
-        <v>436600</v>
+        <v>447500</v>
       </c>
       <c r="J18" s="3">
-        <v>248600</v>
+        <v>254700</v>
       </c>
       <c r="K18" s="3">
         <v>266900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-16200</v>
+        <v>-16600</v>
       </c>
       <c r="E20" s="3">
-        <v>-11900</v>
+        <v>-12200</v>
       </c>
       <c r="F20" s="3">
-        <v>-9700</v>
+        <v>-10000</v>
       </c>
       <c r="G20" s="3">
-        <v>-17300</v>
+        <v>-17700</v>
       </c>
       <c r="H20" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="I20" s="3">
-        <v>-37800</v>
+        <v>-38800</v>
       </c>
       <c r="J20" s="3">
-        <v>-10800</v>
+        <v>-11100</v>
       </c>
       <c r="K20" s="3">
         <v>3300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>663700</v>
+        <v>682200</v>
       </c>
       <c r="E21" s="3">
-        <v>657300</v>
+        <v>675600</v>
       </c>
       <c r="F21" s="3">
-        <v>770900</v>
+        <v>791900</v>
       </c>
       <c r="G21" s="3">
-        <v>395900</v>
+        <v>407500</v>
       </c>
       <c r="H21" s="3">
-        <v>546200</v>
+        <v>561500</v>
       </c>
       <c r="I21" s="3">
-        <v>610300</v>
+        <v>626900</v>
       </c>
       <c r="J21" s="3">
-        <v>421400</v>
+        <v>433000</v>
       </c>
       <c r="K21" s="3">
         <v>438300</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>136200</v>
+        <v>139600</v>
       </c>
       <c r="E22" s="3">
-        <v>129700</v>
+        <v>132900</v>
       </c>
       <c r="F22" s="3">
-        <v>141600</v>
+        <v>145100</v>
       </c>
       <c r="G22" s="3">
-        <v>154500</v>
+        <v>158400</v>
       </c>
       <c r="H22" s="3">
-        <v>182600</v>
+        <v>187200</v>
       </c>
       <c r="I22" s="3">
-        <v>158900</v>
+        <v>162800</v>
       </c>
       <c r="J22" s="3">
-        <v>184800</v>
+        <v>189400</v>
       </c>
       <c r="K22" s="3">
         <v>199600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>211800</v>
+        <v>217100</v>
       </c>
       <c r="E23" s="3">
-        <v>219400</v>
+        <v>224800</v>
       </c>
       <c r="F23" s="3">
-        <v>342600</v>
+        <v>351100</v>
       </c>
       <c r="G23" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="H23" s="3">
-        <v>88600</v>
+        <v>90800</v>
       </c>
       <c r="I23" s="3">
-        <v>239900</v>
+        <v>245900</v>
       </c>
       <c r="J23" s="3">
-        <v>53000</v>
+        <v>54300</v>
       </c>
       <c r="K23" s="3">
         <v>70500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>72400</v>
+        <v>74200</v>
       </c>
       <c r="E24" s="3">
-        <v>-113500</v>
+        <v>-116300</v>
       </c>
       <c r="F24" s="3">
-        <v>59400</v>
+        <v>60900</v>
       </c>
       <c r="G24" s="3">
-        <v>-18400</v>
+        <v>-18800</v>
       </c>
       <c r="H24" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="I24" s="3">
-        <v>34600</v>
+        <v>35400</v>
       </c>
       <c r="J24" s="3">
-        <v>103700</v>
+        <v>106300</v>
       </c>
       <c r="K24" s="3">
         <v>74900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>139400</v>
+        <v>142900</v>
       </c>
       <c r="E26" s="3">
-        <v>332900</v>
+        <v>341100</v>
       </c>
       <c r="F26" s="3">
-        <v>283100</v>
+        <v>290200</v>
       </c>
       <c r="G26" s="3">
-        <v>-18400</v>
+        <v>-18800</v>
       </c>
       <c r="H26" s="3">
-        <v>69200</v>
+        <v>70900</v>
       </c>
       <c r="I26" s="3">
-        <v>205300</v>
+        <v>210400</v>
       </c>
       <c r="J26" s="3">
-        <v>-50800</v>
+        <v>-52100</v>
       </c>
       <c r="K26" s="3">
         <v>-4300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>135100</v>
+        <v>138500</v>
       </c>
       <c r="E27" s="3">
-        <v>325300</v>
+        <v>333400</v>
       </c>
       <c r="F27" s="3">
-        <v>277700</v>
+        <v>284700</v>
       </c>
       <c r="G27" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="H27" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="I27" s="3">
-        <v>203200</v>
+        <v>208200</v>
       </c>
       <c r="J27" s="3">
-        <v>-50800</v>
+        <v>-52100</v>
       </c>
       <c r="K27" s="3">
         <v>-4300</v>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>11</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>16200</v>
+        <v>16600</v>
       </c>
       <c r="E32" s="3">
-        <v>11900</v>
+        <v>12200</v>
       </c>
       <c r="F32" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="G32" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="H32" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="I32" s="3">
-        <v>37800</v>
+        <v>38800</v>
       </c>
       <c r="J32" s="3">
-        <v>10800</v>
+        <v>11100</v>
       </c>
       <c r="K32" s="3">
         <v>-3300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>135100</v>
+        <v>138500</v>
       </c>
       <c r="E33" s="3">
-        <v>325300</v>
+        <v>333400</v>
       </c>
       <c r="F33" s="3">
-        <v>277700</v>
+        <v>284700</v>
       </c>
       <c r="G33" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="H33" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="I33" s="3">
-        <v>203200</v>
+        <v>208200</v>
       </c>
       <c r="J33" s="3">
-        <v>-33500</v>
+        <v>-34300</v>
       </c>
       <c r="K33" s="3">
         <v>-4300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>135100</v>
+        <v>138500</v>
       </c>
       <c r="E35" s="3">
-        <v>325300</v>
+        <v>333400</v>
       </c>
       <c r="F35" s="3">
-        <v>277700</v>
+        <v>284700</v>
       </c>
       <c r="G35" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="H35" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="I35" s="3">
-        <v>203200</v>
+        <v>208200</v>
       </c>
       <c r="J35" s="3">
-        <v>-33500</v>
+        <v>-34300</v>
       </c>
       <c r="K35" s="3">
         <v>-4300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>218300</v>
+        <v>223700</v>
       </c>
       <c r="E41" s="3">
-        <v>179400</v>
+        <v>183900</v>
       </c>
       <c r="F41" s="3">
-        <v>158900</v>
+        <v>162800</v>
       </c>
       <c r="G41" s="3">
-        <v>474400</v>
+        <v>486200</v>
       </c>
       <c r="H41" s="3">
-        <v>198800</v>
+        <v>203800</v>
       </c>
       <c r="I41" s="3">
-        <v>177200</v>
+        <v>181600</v>
       </c>
       <c r="J41" s="3">
-        <v>290700</v>
+        <v>297900</v>
       </c>
       <c r="K41" s="3">
         <v>376500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>520900</v>
+        <v>533900</v>
       </c>
       <c r="E43" s="3">
-        <v>573900</v>
+        <v>588100</v>
       </c>
       <c r="F43" s="3">
-        <v>728400</v>
+        <v>746500</v>
       </c>
       <c r="G43" s="3">
-        <v>432300</v>
+        <v>443000</v>
       </c>
       <c r="H43" s="3">
-        <v>503600</v>
+        <v>516100</v>
       </c>
       <c r="I43" s="3">
-        <v>621400</v>
+        <v>636900</v>
       </c>
       <c r="J43" s="3">
-        <v>444200</v>
+        <v>455200</v>
       </c>
       <c r="K43" s="3">
         <v>375400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1186600</v>
+        <v>1216100</v>
       </c>
       <c r="E44" s="3">
-        <v>1426500</v>
+        <v>1462000</v>
       </c>
       <c r="F44" s="3">
-        <v>1134700</v>
+        <v>1163000</v>
       </c>
       <c r="G44" s="3">
-        <v>629000</v>
+        <v>644600</v>
       </c>
       <c r="H44" s="3">
-        <v>724100</v>
+        <v>742100</v>
       </c>
       <c r="I44" s="3">
-        <v>713300</v>
+        <v>731000</v>
       </c>
       <c r="J44" s="3">
-        <v>694900</v>
+        <v>712200</v>
       </c>
       <c r="K44" s="3">
         <v>641200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="E45" s="3">
-        <v>42100</v>
+        <v>43200</v>
       </c>
       <c r="F45" s="3">
-        <v>72400</v>
+        <v>74200</v>
       </c>
       <c r="G45" s="3">
-        <v>48600</v>
+        <v>49800</v>
       </c>
       <c r="H45" s="3">
-        <v>32400</v>
+        <v>33200</v>
       </c>
       <c r="I45" s="3">
-        <v>45400</v>
+        <v>46500</v>
       </c>
       <c r="J45" s="3">
-        <v>83200</v>
+        <v>85300</v>
       </c>
       <c r="K45" s="3">
         <v>136700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1966900</v>
+        <v>2015800</v>
       </c>
       <c r="E46" s="3">
-        <v>2221900</v>
+        <v>2277200</v>
       </c>
       <c r="F46" s="3">
-        <v>2094400</v>
+        <v>2146500</v>
       </c>
       <c r="G46" s="3">
-        <v>1584300</v>
+        <v>1623700</v>
       </c>
       <c r="H46" s="3">
-        <v>1458900</v>
+        <v>1495300</v>
       </c>
       <c r="I46" s="3">
-        <v>1557300</v>
+        <v>1596100</v>
       </c>
       <c r="J46" s="3">
-        <v>1513000</v>
+        <v>1550600</v>
       </c>
       <c r="K46" s="3">
         <v>1529800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>33500</v>
+        <v>34300</v>
       </c>
       <c r="E47" s="3">
-        <v>46500</v>
+        <v>47600</v>
       </c>
       <c r="F47" s="3">
-        <v>59400</v>
+        <v>60900</v>
       </c>
       <c r="G47" s="3">
-        <v>73500</v>
+        <v>75300</v>
       </c>
       <c r="H47" s="3">
-        <v>65900</v>
+        <v>67600</v>
       </c>
       <c r="I47" s="3">
-        <v>70200</v>
+        <v>72000</v>
       </c>
       <c r="J47" s="3">
-        <v>53000</v>
+        <v>54300</v>
       </c>
       <c r="K47" s="3">
         <v>68400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2212200</v>
+        <v>2267300</v>
       </c>
       <c r="E48" s="3">
-        <v>2179800</v>
+        <v>2234000</v>
       </c>
       <c r="F48" s="3">
-        <v>2105200</v>
+        <v>2157600</v>
       </c>
       <c r="G48" s="3">
-        <v>2059800</v>
+        <v>2111100</v>
       </c>
       <c r="H48" s="3">
-        <v>2221900</v>
+        <v>2277200</v>
       </c>
       <c r="I48" s="3">
-        <v>1800400</v>
+        <v>1845300</v>
       </c>
       <c r="J48" s="3">
-        <v>1639400</v>
+        <v>1680200</v>
       </c>
       <c r="K48" s="3">
         <v>1602500</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>550100</v>
+        <v>563800</v>
       </c>
       <c r="E49" s="3">
-        <v>574900</v>
+        <v>589200</v>
       </c>
       <c r="F49" s="3">
-        <v>550100</v>
+        <v>563800</v>
       </c>
       <c r="G49" s="3">
-        <v>516600</v>
+        <v>529400</v>
       </c>
       <c r="H49" s="3">
-        <v>567400</v>
+        <v>581500</v>
       </c>
       <c r="I49" s="3">
-        <v>531700</v>
+        <v>544900</v>
       </c>
       <c r="J49" s="3">
-        <v>509000</v>
+        <v>521700</v>
       </c>
       <c r="K49" s="3">
         <v>581600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>274500</v>
+        <v>281300</v>
       </c>
       <c r="E52" s="3">
-        <v>316600</v>
+        <v>324500</v>
       </c>
       <c r="F52" s="3">
-        <v>188000</v>
+        <v>192700</v>
       </c>
       <c r="G52" s="3">
-        <v>228000</v>
+        <v>233700</v>
       </c>
       <c r="H52" s="3">
-        <v>207500</v>
+        <v>212700</v>
       </c>
       <c r="I52" s="3">
-        <v>256100</v>
+        <v>262500</v>
       </c>
       <c r="J52" s="3">
-        <v>296100</v>
+        <v>303500</v>
       </c>
       <c r="K52" s="3">
         <v>326600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5037100</v>
+        <v>5162500</v>
       </c>
       <c r="E54" s="3">
-        <v>5339700</v>
+        <v>5472700</v>
       </c>
       <c r="F54" s="3">
-        <v>4997200</v>
+        <v>5121500</v>
       </c>
       <c r="G54" s="3">
-        <v>4462200</v>
+        <v>4573300</v>
       </c>
       <c r="H54" s="3">
-        <v>4521600</v>
+        <v>4634200</v>
       </c>
       <c r="I54" s="3">
-        <v>4215800</v>
+        <v>4320700</v>
       </c>
       <c r="J54" s="3">
-        <v>4010500</v>
+        <v>4110300</v>
       </c>
       <c r="K54" s="3">
         <v>4108900</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1006100</v>
+        <v>1031200</v>
       </c>
       <c r="E57" s="3">
-        <v>1248200</v>
+        <v>1279300</v>
       </c>
       <c r="F57" s="3">
-        <v>1150900</v>
+        <v>1179600</v>
       </c>
       <c r="G57" s="3">
-        <v>676500</v>
+        <v>693400</v>
       </c>
       <c r="H57" s="3">
-        <v>768400</v>
+        <v>787500</v>
       </c>
       <c r="I57" s="3">
-        <v>740300</v>
+        <v>758700</v>
       </c>
       <c r="J57" s="3">
-        <v>774900</v>
+        <v>794100</v>
       </c>
       <c r="K57" s="3">
         <v>680300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>58400</v>
+        <v>59800</v>
       </c>
       <c r="E58" s="3">
-        <v>159900</v>
+        <v>163900</v>
       </c>
       <c r="F58" s="3">
-        <v>278800</v>
+        <v>285800</v>
       </c>
       <c r="G58" s="3">
-        <v>99400</v>
+        <v>101900</v>
       </c>
       <c r="H58" s="3">
-        <v>217200</v>
+        <v>222600</v>
       </c>
       <c r="I58" s="3">
-        <v>61600</v>
+        <v>63100</v>
       </c>
       <c r="J58" s="3">
-        <v>114600</v>
+        <v>117400</v>
       </c>
       <c r="K58" s="3">
         <v>116100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>435500</v>
+        <v>446400</v>
       </c>
       <c r="E59" s="3">
-        <v>421500</v>
+        <v>432000</v>
       </c>
       <c r="F59" s="3">
-        <v>422600</v>
+        <v>433100</v>
       </c>
       <c r="G59" s="3">
-        <v>397700</v>
+        <v>407600</v>
       </c>
       <c r="H59" s="3">
-        <v>389100</v>
+        <v>398700</v>
       </c>
       <c r="I59" s="3">
-        <v>429000</v>
+        <v>439700</v>
       </c>
       <c r="J59" s="3">
-        <v>310200</v>
+        <v>317900</v>
       </c>
       <c r="K59" s="3">
         <v>326600</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1500000</v>
+        <v>1537300</v>
       </c>
       <c r="E60" s="3">
-        <v>1829600</v>
+        <v>1875200</v>
       </c>
       <c r="F60" s="3">
-        <v>1852300</v>
+        <v>1898400</v>
       </c>
       <c r="G60" s="3">
-        <v>1173600</v>
+        <v>1202900</v>
       </c>
       <c r="H60" s="3">
-        <v>1374700</v>
+        <v>1408900</v>
       </c>
       <c r="I60" s="3">
-        <v>1230900</v>
+        <v>1261600</v>
       </c>
       <c r="J60" s="3">
-        <v>1199600</v>
+        <v>1229400</v>
       </c>
       <c r="K60" s="3">
         <v>1123000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1960400</v>
+        <v>2009200</v>
       </c>
       <c r="E61" s="3">
-        <v>2062000</v>
+        <v>2113300</v>
       </c>
       <c r="F61" s="3">
-        <v>2022000</v>
+        <v>2072300</v>
       </c>
       <c r="G61" s="3">
-        <v>2484500</v>
+        <v>2546400</v>
       </c>
       <c r="H61" s="3">
-        <v>2334300</v>
+        <v>2392400</v>
       </c>
       <c r="I61" s="3">
-        <v>2263000</v>
+        <v>2319300</v>
       </c>
       <c r="J61" s="3">
-        <v>2184100</v>
+        <v>2238500</v>
       </c>
       <c r="K61" s="3">
         <v>2561700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>643000</v>
+        <v>659000</v>
       </c>
       <c r="E62" s="3">
-        <v>624600</v>
+        <v>640200</v>
       </c>
       <c r="F62" s="3">
-        <v>808400</v>
+        <v>828500</v>
       </c>
       <c r="G62" s="3">
-        <v>913200</v>
+        <v>935900</v>
       </c>
       <c r="H62" s="3">
-        <v>904500</v>
+        <v>927100</v>
       </c>
       <c r="I62" s="3">
-        <v>845100</v>
+        <v>866100</v>
       </c>
       <c r="J62" s="3">
-        <v>971500</v>
+        <v>995700</v>
       </c>
       <c r="K62" s="3">
         <v>1042700</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4126100</v>
+        <v>4228800</v>
       </c>
       <c r="E66" s="3">
-        <v>4549700</v>
+        <v>4663000</v>
       </c>
       <c r="F66" s="3">
-        <v>4701000</v>
+        <v>4818100</v>
       </c>
       <c r="G66" s="3">
-        <v>4586500</v>
+        <v>4700700</v>
       </c>
       <c r="H66" s="3">
-        <v>4625400</v>
+        <v>4740500</v>
       </c>
       <c r="I66" s="3">
-        <v>4347700</v>
+        <v>4455900</v>
       </c>
       <c r="J66" s="3">
-        <v>4363900</v>
+        <v>4472500</v>
       </c>
       <c r="K66" s="3">
         <v>4737100</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>440900</v>
+        <v>451900</v>
       </c>
       <c r="E72" s="3">
-        <v>299400</v>
+        <v>306800</v>
       </c>
       <c r="F72" s="3">
-        <v>-177200</v>
+        <v>-181600</v>
       </c>
       <c r="G72" s="3">
-        <v>-577100</v>
+        <v>-591500</v>
       </c>
       <c r="H72" s="3">
-        <v>-554400</v>
+        <v>-568200</v>
       </c>
       <c r="I72" s="3">
-        <v>-583600</v>
+        <v>-598100</v>
       </c>
       <c r="J72" s="3">
-        <v>-817000</v>
+        <v>-837300</v>
       </c>
       <c r="K72" s="3">
         <v>-799600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>911000</v>
+        <v>933700</v>
       </c>
       <c r="E76" s="3">
-        <v>790000</v>
+        <v>809700</v>
       </c>
       <c r="F76" s="3">
-        <v>296100</v>
+        <v>303500</v>
       </c>
       <c r="G76" s="3">
-        <v>-124300</v>
+        <v>-127400</v>
       </c>
       <c r="H76" s="3">
-        <v>-103700</v>
+        <v>-106300</v>
       </c>
       <c r="I76" s="3">
-        <v>-131800</v>
+        <v>-135100</v>
       </c>
       <c r="J76" s="3">
-        <v>-353400</v>
+        <v>-362200</v>
       </c>
       <c r="K76" s="3">
         <v>-628200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>135100</v>
+        <v>138500</v>
       </c>
       <c r="E81" s="3">
-        <v>325300</v>
+        <v>333400</v>
       </c>
       <c r="F81" s="3">
-        <v>277700</v>
+        <v>284700</v>
       </c>
       <c r="G81" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="H81" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="I81" s="3">
-        <v>203200</v>
+        <v>208200</v>
       </c>
       <c r="J81" s="3">
-        <v>-33500</v>
+        <v>-34300</v>
       </c>
       <c r="K81" s="3">
         <v>-4300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>317700</v>
+        <v>325600</v>
       </c>
       <c r="E83" s="3">
-        <v>310200</v>
+        <v>317900</v>
       </c>
       <c r="F83" s="3">
-        <v>288500</v>
+        <v>295700</v>
       </c>
       <c r="G83" s="3">
-        <v>279900</v>
+        <v>286900</v>
       </c>
       <c r="H83" s="3">
-        <v>276700</v>
+        <v>283500</v>
       </c>
       <c r="I83" s="3">
-        <v>212900</v>
+        <v>218200</v>
       </c>
       <c r="J83" s="3">
-        <v>184800</v>
+        <v>189400</v>
       </c>
       <c r="K83" s="3">
         <v>168200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>546800</v>
+        <v>560400</v>
       </c>
       <c r="E89" s="3">
-        <v>486300</v>
+        <v>498400</v>
       </c>
       <c r="F89" s="3">
-        <v>385800</v>
+        <v>395400</v>
       </c>
       <c r="G89" s="3">
-        <v>361000</v>
+        <v>369900</v>
       </c>
       <c r="H89" s="3">
-        <v>483100</v>
+        <v>495100</v>
       </c>
       <c r="I89" s="3">
-        <v>71300</v>
+        <v>73100</v>
       </c>
       <c r="J89" s="3">
-        <v>172900</v>
+        <v>177200</v>
       </c>
       <c r="K89" s="3">
         <v>95500</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-364200</v>
+        <v>-373300</v>
       </c>
       <c r="E91" s="3">
-        <v>-295000</v>
+        <v>-302400</v>
       </c>
       <c r="F91" s="3">
-        <v>-250700</v>
+        <v>-257000</v>
       </c>
       <c r="G91" s="3">
-        <v>-196700</v>
+        <v>-201600</v>
       </c>
       <c r="H91" s="3">
-        <v>-292900</v>
+        <v>-300200</v>
       </c>
       <c r="I91" s="3">
-        <v>-299400</v>
+        <v>-306800</v>
       </c>
       <c r="J91" s="3">
-        <v>-298300</v>
+        <v>-305700</v>
       </c>
       <c r="K91" s="3">
         <v>-385200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-311200</v>
+        <v>-319000</v>
       </c>
       <c r="E94" s="3">
-        <v>-291800</v>
+        <v>-299100</v>
       </c>
       <c r="F94" s="3">
-        <v>-238800</v>
+        <v>-244800</v>
       </c>
       <c r="G94" s="3">
-        <v>-190200</v>
+        <v>-194900</v>
       </c>
       <c r="H94" s="3">
-        <v>-381500</v>
+        <v>-391000</v>
       </c>
       <c r="I94" s="3">
-        <v>-98300</v>
+        <v>-100800</v>
       </c>
       <c r="J94" s="3">
-        <v>-315600</v>
+        <v>-323400</v>
       </c>
       <c r="K94" s="3">
         <v>-396000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-196700</v>
+        <v>-201600</v>
       </c>
       <c r="E100" s="3">
-        <v>-176200</v>
+        <v>-180500</v>
       </c>
       <c r="F100" s="3">
-        <v>-470100</v>
+        <v>-481800</v>
       </c>
       <c r="G100" s="3">
-        <v>109200</v>
+        <v>111900</v>
       </c>
       <c r="H100" s="3">
-        <v>-82100</v>
+        <v>-84200</v>
       </c>
       <c r="I100" s="3">
-        <v>-88600</v>
+        <v>-90800</v>
       </c>
       <c r="J100" s="3">
-        <v>65900</v>
+        <v>67600</v>
       </c>
       <c r="K100" s="3">
         <v>157300</v>
@@ -4458,10 +4458,10 @@
         <v>2200</v>
       </c>
       <c r="F101" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="G101" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="H101" s="3">
         <v>2200</v>
@@ -4470,7 +4470,7 @@
         <v>2200</v>
       </c>
       <c r="J101" s="3">
-        <v>-7600</v>
+        <v>-7800</v>
       </c>
       <c r="K101" s="3">
         <v>3300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>37800</v>
+        <v>38800</v>
       </c>
       <c r="E102" s="3">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="F102" s="3">
-        <v>-315600</v>
+        <v>-323400</v>
       </c>
       <c r="G102" s="3">
-        <v>275600</v>
+        <v>282400</v>
       </c>
       <c r="H102" s="3">
-        <v>21600</v>
+        <v>22200</v>
       </c>
       <c r="I102" s="3">
-        <v>-113500</v>
+        <v>-116300</v>
       </c>
       <c r="J102" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="K102" s="3">
         <v>-140000</v>

--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>CSTM</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8017900</v>
+        <v>8001500</v>
       </c>
       <c r="E8" s="3">
-        <v>8993700</v>
+        <v>8678000</v>
       </c>
       <c r="F8" s="3">
-        <v>6814000</v>
+        <v>6996500</v>
       </c>
       <c r="G8" s="3">
-        <v>5408400</v>
+        <v>5973100</v>
       </c>
       <c r="H8" s="3">
-        <v>6542600</v>
+        <v>6628900</v>
       </c>
       <c r="I8" s="3">
-        <v>6297800</v>
+        <v>6510200</v>
       </c>
       <c r="J8" s="3">
-        <v>5800500</v>
+        <v>6288400</v>
       </c>
       <c r="K8" s="3">
         <v>5146200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7231500</v>
+        <v>7216800</v>
       </c>
       <c r="E9" s="3">
-        <v>8249400</v>
+        <v>7959800</v>
       </c>
       <c r="F9" s="3">
-        <v>6078500</v>
+        <v>6241300</v>
       </c>
       <c r="G9" s="3">
-        <v>4865700</v>
+        <v>5373700</v>
       </c>
       <c r="H9" s="3">
-        <v>5875800</v>
+        <v>5953300</v>
       </c>
       <c r="I9" s="3">
-        <v>5701900</v>
+        <v>5894200</v>
       </c>
       <c r="J9" s="3">
-        <v>5203500</v>
+        <v>5622000</v>
       </c>
       <c r="K9" s="3">
         <v>4586300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>786400</v>
+        <v>784800</v>
       </c>
       <c r="E10" s="3">
-        <v>744300</v>
+        <v>718200</v>
       </c>
       <c r="F10" s="3">
-        <v>735400</v>
+        <v>755100</v>
       </c>
       <c r="G10" s="3">
-        <v>542700</v>
+        <v>599400</v>
       </c>
       <c r="H10" s="3">
-        <v>666800</v>
+        <v>675600</v>
       </c>
       <c r="I10" s="3">
-        <v>595900</v>
+        <v>616000</v>
       </c>
       <c r="J10" s="3">
-        <v>597000</v>
+        <v>666400</v>
       </c>
       <c r="K10" s="3">
         <v>559900</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>52100</v>
+        <v>57500</v>
       </c>
       <c r="E12" s="3">
-        <v>47600</v>
+        <v>51300</v>
       </c>
       <c r="F12" s="3">
-        <v>37700</v>
+        <v>44400</v>
       </c>
       <c r="G12" s="3">
-        <v>37700</v>
+        <v>47700</v>
       </c>
       <c r="H12" s="3">
-        <v>46500</v>
+        <v>53900</v>
       </c>
       <c r="I12" s="3">
-        <v>39900</v>
+        <v>45800</v>
       </c>
       <c r="J12" s="3">
-        <v>36600</v>
+        <v>43200</v>
       </c>
       <c r="K12" s="3">
         <v>34700</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-32100</v>
       </c>
       <c r="E14" s="3">
-        <v>-50900</v>
+        <v>-44900</v>
       </c>
       <c r="F14" s="3">
-        <v>68700</v>
+        <v>73900</v>
       </c>
       <c r="G14" s="3">
-        <v>70900</v>
+        <v>75800</v>
       </c>
       <c r="H14" s="3">
-        <v>3300</v>
+        <v>7900</v>
       </c>
       <c r="I14" s="3">
-        <v>-38800</v>
+        <v>-248500</v>
       </c>
       <c r="J14" s="3">
-        <v>83100</v>
+        <v>93700</v>
       </c>
       <c r="K14" s="3">
         <v>5400</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>18800</v>
+        <v>284100</v>
       </c>
       <c r="E15" s="3">
-        <v>18800</v>
+        <v>264000</v>
       </c>
       <c r="F15" s="3">
-        <v>24400</v>
+        <v>303700</v>
       </c>
       <c r="G15" s="3">
-        <v>21000</v>
+        <v>316800</v>
       </c>
       <c r="H15" s="3">
-        <v>21000</v>
+        <v>287300</v>
       </c>
       <c r="I15" s="3">
-        <v>14400</v>
+        <v>225600</v>
       </c>
       <c r="J15" s="3">
-        <v>12200</v>
+        <v>205300</v>
       </c>
       <c r="K15" s="3">
         <v>8700</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7644700</v>
+        <v>7681000</v>
       </c>
       <c r="E17" s="3">
-        <v>8623800</v>
+        <v>8383000</v>
       </c>
       <c r="F17" s="3">
-        <v>6307800</v>
+        <v>6431300</v>
       </c>
       <c r="G17" s="3">
-        <v>5270000</v>
+        <v>5734600</v>
       </c>
       <c r="H17" s="3">
-        <v>6260200</v>
+        <v>6362900</v>
       </c>
       <c r="I17" s="3">
-        <v>5850300</v>
+        <v>6328100</v>
       </c>
       <c r="J17" s="3">
-        <v>5545800</v>
+        <v>5913800</v>
       </c>
       <c r="K17" s="3">
         <v>4879200</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>373300</v>
+        <v>320500</v>
       </c>
       <c r="E18" s="3">
-        <v>369900</v>
+        <v>295000</v>
       </c>
       <c r="F18" s="3">
-        <v>506200</v>
+        <v>565200</v>
       </c>
       <c r="G18" s="3">
-        <v>138500</v>
+        <v>238500</v>
       </c>
       <c r="H18" s="3">
-        <v>282400</v>
+        <v>266000</v>
       </c>
       <c r="I18" s="3">
-        <v>447500</v>
+        <v>182000</v>
       </c>
       <c r="J18" s="3">
-        <v>254700</v>
+        <v>374600</v>
       </c>
       <c r="K18" s="3">
         <v>266900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-16600</v>
+        <v>26500</v>
       </c>
       <c r="E20" s="3">
-        <v>-12200</v>
+        <v>16000</v>
       </c>
       <c r="F20" s="3">
-        <v>-10000</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="3">
-        <v>-17700</v>
+        <v>44000</v>
       </c>
       <c r="H20" s="3">
-        <v>-4400</v>
+        <v>10100</v>
       </c>
       <c r="I20" s="3">
-        <v>-38800</v>
+        <v>48100</v>
       </c>
       <c r="J20" s="3">
-        <v>-11100</v>
+        <v>58800</v>
       </c>
       <c r="K20" s="3">
         <v>3300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>682200</v>
+        <v>578100</v>
       </c>
       <c r="E21" s="3">
-        <v>675600</v>
+        <v>542900</v>
       </c>
       <c r="F21" s="3">
-        <v>791900</v>
+        <v>870000</v>
       </c>
       <c r="G21" s="3">
-        <v>407500</v>
+        <v>511300</v>
       </c>
       <c r="H21" s="3">
-        <v>561500</v>
+        <v>543100</v>
       </c>
       <c r="I21" s="3">
-        <v>626900</v>
+        <v>359500</v>
       </c>
       <c r="J21" s="3">
-        <v>433000</v>
+        <v>521100</v>
       </c>
       <c r="K21" s="3">
         <v>438300</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>139600</v>
+        <v>109400</v>
       </c>
       <c r="E22" s="3">
-        <v>132900</v>
+        <v>106900</v>
       </c>
       <c r="F22" s="3">
-        <v>145100</v>
+        <v>131900</v>
       </c>
       <c r="G22" s="3">
-        <v>158400</v>
+        <v>160200</v>
       </c>
       <c r="H22" s="3">
-        <v>187200</v>
+        <v>156000</v>
       </c>
       <c r="I22" s="3">
-        <v>162800</v>
+        <v>136200</v>
       </c>
       <c r="J22" s="3">
-        <v>189400</v>
+        <v>171700</v>
       </c>
       <c r="K22" s="3">
         <v>199600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>217100</v>
+        <v>216600</v>
       </c>
       <c r="E23" s="3">
-        <v>224800</v>
+        <v>216900</v>
       </c>
       <c r="F23" s="3">
-        <v>351100</v>
+        <v>360500</v>
       </c>
       <c r="G23" s="3">
-        <v>-37700</v>
+        <v>-41600</v>
       </c>
       <c r="H23" s="3">
-        <v>90800</v>
+        <v>92000</v>
       </c>
       <c r="I23" s="3">
-        <v>245900</v>
+        <v>254200</v>
       </c>
       <c r="J23" s="3">
-        <v>54300</v>
+        <v>58800</v>
       </c>
       <c r="K23" s="3">
         <v>70500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>74200</v>
+        <v>74100</v>
       </c>
       <c r="E24" s="3">
-        <v>-116300</v>
+        <v>-112200</v>
       </c>
       <c r="F24" s="3">
-        <v>60900</v>
+        <v>62500</v>
       </c>
       <c r="G24" s="3">
-        <v>-18800</v>
+        <v>-20800</v>
       </c>
       <c r="H24" s="3">
-        <v>19900</v>
+        <v>20200</v>
       </c>
       <c r="I24" s="3">
-        <v>35400</v>
+        <v>36600</v>
       </c>
       <c r="J24" s="3">
-        <v>106300</v>
+        <v>96100</v>
       </c>
       <c r="K24" s="3">
         <v>74900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>142900</v>
+        <v>142600</v>
       </c>
       <c r="E26" s="3">
-        <v>341100</v>
+        <v>329200</v>
       </c>
       <c r="F26" s="3">
-        <v>290200</v>
+        <v>298000</v>
       </c>
       <c r="G26" s="3">
-        <v>-18800</v>
+        <v>-20800</v>
       </c>
       <c r="H26" s="3">
-        <v>70900</v>
+        <v>71800</v>
       </c>
       <c r="I26" s="3">
-        <v>210400</v>
+        <v>217500</v>
       </c>
       <c r="J26" s="3">
-        <v>-52100</v>
+        <v>-37200</v>
       </c>
       <c r="K26" s="3">
         <v>-4300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>138500</v>
+        <v>138200</v>
       </c>
       <c r="E27" s="3">
-        <v>333400</v>
+        <v>321700</v>
       </c>
       <c r="F27" s="3">
-        <v>284700</v>
+        <v>292300</v>
       </c>
       <c r="G27" s="3">
-        <v>-23300</v>
+        <v>-25700</v>
       </c>
       <c r="H27" s="3">
-        <v>65300</v>
+        <v>66200</v>
       </c>
       <c r="I27" s="3">
-        <v>208200</v>
+        <v>215300</v>
       </c>
       <c r="J27" s="3">
-        <v>-52100</v>
+        <v>-37200</v>
       </c>
       <c r="K27" s="3">
         <v>-4300</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>11</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>11</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>16600</v>
+        <v>-26500</v>
       </c>
       <c r="E32" s="3">
-        <v>12200</v>
+        <v>-16000</v>
       </c>
       <c r="F32" s="3">
-        <v>10000</v>
+        <v>1100</v>
       </c>
       <c r="G32" s="3">
-        <v>17700</v>
+        <v>-44000</v>
       </c>
       <c r="H32" s="3">
-        <v>4400</v>
+        <v>-10100</v>
       </c>
       <c r="I32" s="3">
-        <v>38800</v>
+        <v>-48100</v>
       </c>
       <c r="J32" s="3">
-        <v>11100</v>
+        <v>-58800</v>
       </c>
       <c r="K32" s="3">
         <v>-3300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>138500</v>
+        <v>138200</v>
       </c>
       <c r="E33" s="3">
-        <v>333400</v>
+        <v>321700</v>
       </c>
       <c r="F33" s="3">
-        <v>284700</v>
+        <v>292300</v>
       </c>
       <c r="G33" s="3">
-        <v>-23300</v>
+        <v>-25700</v>
       </c>
       <c r="H33" s="3">
-        <v>65300</v>
+        <v>66200</v>
       </c>
       <c r="I33" s="3">
-        <v>208200</v>
+        <v>215300</v>
       </c>
       <c r="J33" s="3">
-        <v>-34300</v>
+        <v>-37200</v>
       </c>
       <c r="K33" s="3">
         <v>-4300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>138500</v>
+        <v>138200</v>
       </c>
       <c r="E35" s="3">
-        <v>333400</v>
+        <v>321700</v>
       </c>
       <c r="F35" s="3">
-        <v>284700</v>
+        <v>292300</v>
       </c>
       <c r="G35" s="3">
-        <v>-23300</v>
+        <v>-25700</v>
       </c>
       <c r="H35" s="3">
-        <v>65300</v>
+        <v>66200</v>
       </c>
       <c r="I35" s="3">
-        <v>208200</v>
+        <v>215300</v>
       </c>
       <c r="J35" s="3">
-        <v>-34300</v>
+        <v>-37200</v>
       </c>
       <c r="K35" s="3">
         <v>-4300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>223700</v>
+        <v>223300</v>
       </c>
       <c r="E41" s="3">
-        <v>183900</v>
+        <v>177400</v>
       </c>
       <c r="F41" s="3">
-        <v>162800</v>
+        <v>167200</v>
       </c>
       <c r="G41" s="3">
-        <v>486200</v>
+        <v>537000</v>
       </c>
       <c r="H41" s="3">
-        <v>203800</v>
+        <v>206500</v>
       </c>
       <c r="I41" s="3">
-        <v>181600</v>
+        <v>187800</v>
       </c>
       <c r="J41" s="3">
-        <v>297900</v>
+        <v>323000</v>
       </c>
       <c r="K41" s="3">
         <v>376500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>533900</v>
+        <v>532800</v>
       </c>
       <c r="E43" s="3">
-        <v>588100</v>
+        <v>567500</v>
       </c>
       <c r="F43" s="3">
-        <v>746500</v>
+        <v>766500</v>
       </c>
       <c r="G43" s="3">
-        <v>443000</v>
+        <v>489300</v>
       </c>
       <c r="H43" s="3">
-        <v>516100</v>
+        <v>522900</v>
       </c>
       <c r="I43" s="3">
-        <v>636900</v>
+        <v>660600</v>
       </c>
       <c r="J43" s="3">
-        <v>455200</v>
+        <v>495900</v>
       </c>
       <c r="K43" s="3">
         <v>375400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1216100</v>
+        <v>1213700</v>
       </c>
       <c r="E44" s="3">
-        <v>1462000</v>
+        <v>1410700</v>
       </c>
       <c r="F44" s="3">
-        <v>1163000</v>
+        <v>1194100</v>
       </c>
       <c r="G44" s="3">
-        <v>644600</v>
+        <v>711900</v>
       </c>
       <c r="H44" s="3">
-        <v>742100</v>
+        <v>751900</v>
       </c>
       <c r="I44" s="3">
-        <v>731000</v>
+        <v>755700</v>
       </c>
       <c r="J44" s="3">
-        <v>712200</v>
+        <v>772100</v>
       </c>
       <c r="K44" s="3">
         <v>641200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>42100</v>
+        <v>33200</v>
       </c>
       <c r="E45" s="3">
-        <v>43200</v>
+        <v>48100</v>
       </c>
       <c r="F45" s="3">
-        <v>74200</v>
+        <v>66000</v>
       </c>
       <c r="G45" s="3">
-        <v>49800</v>
+        <v>47700</v>
       </c>
       <c r="H45" s="3">
-        <v>33200</v>
+        <v>24700</v>
       </c>
       <c r="I45" s="3">
-        <v>46500</v>
+        <v>32100</v>
       </c>
       <c r="J45" s="3">
-        <v>85300</v>
+        <v>80500</v>
       </c>
       <c r="K45" s="3">
         <v>136700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2015800</v>
+        <v>2011700</v>
       </c>
       <c r="E46" s="3">
-        <v>2277200</v>
+        <v>2212200</v>
       </c>
       <c r="F46" s="3">
-        <v>2146500</v>
+        <v>2204000</v>
       </c>
       <c r="G46" s="3">
-        <v>1623700</v>
+        <v>1793300</v>
       </c>
       <c r="H46" s="3">
-        <v>1495300</v>
+        <v>1515000</v>
       </c>
       <c r="I46" s="3">
-        <v>1596100</v>
+        <v>1649900</v>
       </c>
       <c r="J46" s="3">
-        <v>1550600</v>
+        <v>1681100</v>
       </c>
       <c r="K46" s="3">
         <v>1529800</v>
@@ -2262,26 +2262,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>34300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>47600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>60900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>75300</v>
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="H47" s="3">
-        <v>67600</v>
+        <v>1100</v>
       </c>
       <c r="I47" s="3">
-        <v>72000</v>
+        <v>1100</v>
       </c>
       <c r="J47" s="3">
-        <v>54300</v>
+        <v>1200</v>
       </c>
       <c r="K47" s="3">
         <v>68400</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2267300</v>
+        <v>2262600</v>
       </c>
       <c r="E48" s="3">
-        <v>2234000</v>
+        <v>2155600</v>
       </c>
       <c r="F48" s="3">
-        <v>2157600</v>
+        <v>2215400</v>
       </c>
       <c r="G48" s="3">
-        <v>2111100</v>
+        <v>2331500</v>
       </c>
       <c r="H48" s="3">
-        <v>2277200</v>
+        <v>2307300</v>
       </c>
       <c r="I48" s="3">
-        <v>1845300</v>
+        <v>1907500</v>
       </c>
       <c r="J48" s="3">
-        <v>1680200</v>
+        <v>1821600</v>
       </c>
       <c r="K48" s="3">
         <v>1602500</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>563800</v>
+        <v>562600</v>
       </c>
       <c r="E49" s="3">
+        <v>568600</v>
+      </c>
+      <c r="F49" s="3">
+        <v>578900</v>
+      </c>
+      <c r="G49" s="3">
+        <v>584700</v>
+      </c>
+      <c r="H49" s="3">
         <v>589200</v>
       </c>
-      <c r="F49" s="3">
-        <v>563800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>529400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>581500</v>
-      </c>
       <c r="I49" s="3">
-        <v>544900</v>
+        <v>563300</v>
       </c>
       <c r="J49" s="3">
-        <v>521700</v>
+        <v>565600</v>
       </c>
       <c r="K49" s="3">
         <v>581600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>281300</v>
+        <v>18800</v>
       </c>
       <c r="E52" s="3">
-        <v>324500</v>
+        <v>38500</v>
       </c>
       <c r="F52" s="3">
-        <v>192700</v>
+        <v>54600</v>
       </c>
       <c r="G52" s="3">
-        <v>233700</v>
+        <v>77100</v>
       </c>
       <c r="H52" s="3">
-        <v>212700</v>
+        <v>57200</v>
       </c>
       <c r="I52" s="3">
-        <v>262500</v>
+        <v>49200</v>
       </c>
       <c r="J52" s="3">
-        <v>303500</v>
+        <v>51600</v>
       </c>
       <c r="K52" s="3">
         <v>326600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5162500</v>
+        <v>5152000</v>
       </c>
       <c r="E54" s="3">
-        <v>5472700</v>
+        <v>5280500</v>
       </c>
       <c r="F54" s="3">
-        <v>5121500</v>
+        <v>5258700</v>
       </c>
       <c r="G54" s="3">
-        <v>4573300</v>
+        <v>5050800</v>
       </c>
       <c r="H54" s="3">
-        <v>4634200</v>
+        <v>4695300</v>
       </c>
       <c r="I54" s="3">
-        <v>4320700</v>
+        <v>4466500</v>
       </c>
       <c r="J54" s="3">
-        <v>4110300</v>
+        <v>4456100</v>
       </c>
       <c r="K54" s="3">
         <v>4108900</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1031200</v>
+        <v>1029100</v>
       </c>
       <c r="E57" s="3">
-        <v>1279300</v>
+        <v>1234400</v>
       </c>
       <c r="F57" s="3">
-        <v>1179600</v>
+        <v>1211200</v>
       </c>
       <c r="G57" s="3">
-        <v>693400</v>
+        <v>765700</v>
       </c>
       <c r="H57" s="3">
-        <v>787500</v>
+        <v>797900</v>
       </c>
       <c r="I57" s="3">
-        <v>758700</v>
+        <v>784300</v>
       </c>
       <c r="J57" s="3">
-        <v>794100</v>
+        <v>861000</v>
       </c>
       <c r="K57" s="3">
         <v>680300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>59800</v>
+        <v>59700</v>
       </c>
       <c r="E58" s="3">
-        <v>163900</v>
+        <v>158200</v>
       </c>
       <c r="F58" s="3">
-        <v>285800</v>
+        <v>293400</v>
       </c>
       <c r="G58" s="3">
-        <v>101900</v>
+        <v>126000</v>
       </c>
       <c r="H58" s="3">
-        <v>222600</v>
+        <v>230100</v>
       </c>
       <c r="I58" s="3">
-        <v>63100</v>
+        <v>68700</v>
       </c>
       <c r="J58" s="3">
-        <v>117400</v>
+        <v>132100</v>
       </c>
       <c r="K58" s="3">
         <v>116100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>446400</v>
+        <v>195600</v>
       </c>
       <c r="E59" s="3">
-        <v>432000</v>
+        <v>200900</v>
       </c>
       <c r="F59" s="3">
-        <v>433100</v>
+        <v>216100</v>
       </c>
       <c r="G59" s="3">
-        <v>407600</v>
+        <v>243400</v>
       </c>
       <c r="H59" s="3">
-        <v>398700</v>
+        <v>191900</v>
       </c>
       <c r="I59" s="3">
-        <v>439700</v>
+        <v>249600</v>
       </c>
       <c r="J59" s="3">
-        <v>317900</v>
+        <v>134500</v>
       </c>
       <c r="K59" s="3">
         <v>326600</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1537300</v>
+        <v>1534200</v>
       </c>
       <c r="E60" s="3">
-        <v>1875200</v>
+        <v>1820000</v>
       </c>
       <c r="F60" s="3">
-        <v>1898400</v>
+        <v>1949300</v>
       </c>
       <c r="G60" s="3">
-        <v>1202900</v>
+        <v>1328400</v>
       </c>
       <c r="H60" s="3">
-        <v>1408900</v>
+        <v>1427400</v>
       </c>
       <c r="I60" s="3">
-        <v>1261600</v>
+        <v>1304100</v>
       </c>
       <c r="J60" s="3">
-        <v>1229400</v>
+        <v>1332900</v>
       </c>
       <c r="K60" s="3">
         <v>1123000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2009200</v>
+        <v>2005100</v>
       </c>
       <c r="E61" s="3">
-        <v>2113300</v>
+        <v>2039100</v>
       </c>
       <c r="F61" s="3">
-        <v>2072300</v>
+        <v>2127800</v>
       </c>
       <c r="G61" s="3">
-        <v>2546400</v>
+        <v>2853800</v>
       </c>
       <c r="H61" s="3">
-        <v>2392400</v>
+        <v>2429600</v>
       </c>
       <c r="I61" s="3">
-        <v>2319300</v>
+        <v>2410100</v>
       </c>
       <c r="J61" s="3">
-        <v>2238500</v>
+        <v>2471200</v>
       </c>
       <c r="K61" s="3">
         <v>2561700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>659000</v>
+        <v>140400</v>
       </c>
       <c r="E62" s="3">
-        <v>640200</v>
+        <v>135700</v>
       </c>
       <c r="F62" s="3">
-        <v>828500</v>
+        <v>149000</v>
       </c>
       <c r="G62" s="3">
-        <v>935900</v>
+        <v>163900</v>
       </c>
       <c r="H62" s="3">
-        <v>927100</v>
+        <v>148100</v>
       </c>
       <c r="I62" s="3">
-        <v>866100</v>
+        <v>148800</v>
       </c>
       <c r="J62" s="3">
-        <v>995700</v>
+        <v>166900</v>
       </c>
       <c r="K62" s="3">
         <v>1042700</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4228800</v>
+        <v>4197000</v>
       </c>
       <c r="E66" s="3">
-        <v>4663000</v>
+        <v>4476900</v>
       </c>
       <c r="F66" s="3">
-        <v>4818100</v>
+        <v>4927800</v>
       </c>
       <c r="G66" s="3">
-        <v>4700700</v>
+        <v>5174300</v>
       </c>
       <c r="H66" s="3">
-        <v>4740500</v>
+        <v>4790700</v>
       </c>
       <c r="I66" s="3">
-        <v>4455900</v>
+        <v>4597000</v>
       </c>
       <c r="J66" s="3">
-        <v>4472500</v>
+        <v>4839100</v>
       </c>
       <c r="K66" s="3">
         <v>4737100</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>451900</v>
+        <v>302900</v>
       </c>
       <c r="E72" s="3">
-        <v>306800</v>
+        <v>158200</v>
       </c>
       <c r="F72" s="3">
-        <v>-181600</v>
+        <v>-174000</v>
       </c>
       <c r="G72" s="3">
-        <v>-591500</v>
+        <v>-501500</v>
       </c>
       <c r="H72" s="3">
-        <v>-568200</v>
+        <v>-436500</v>
       </c>
       <c r="I72" s="3">
-        <v>-598100</v>
+        <v>-512900</v>
       </c>
       <c r="J72" s="3">
-        <v>-837300</v>
+        <v>-761300</v>
       </c>
       <c r="K72" s="3">
         <v>-799600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>933700</v>
+        <v>931800</v>
       </c>
       <c r="E76" s="3">
-        <v>809700</v>
+        <v>781200</v>
       </c>
       <c r="F76" s="3">
-        <v>303500</v>
+        <v>311600</v>
       </c>
       <c r="G76" s="3">
-        <v>-127400</v>
+        <v>-140700</v>
       </c>
       <c r="H76" s="3">
-        <v>-106300</v>
+        <v>-107700</v>
       </c>
       <c r="I76" s="3">
-        <v>-135100</v>
+        <v>-139700</v>
       </c>
       <c r="J76" s="3">
-        <v>-362200</v>
+        <v>-392700</v>
       </c>
       <c r="K76" s="3">
         <v>-628200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>138500</v>
+        <v>138200</v>
       </c>
       <c r="E81" s="3">
-        <v>333400</v>
+        <v>321700</v>
       </c>
       <c r="F81" s="3">
-        <v>284700</v>
+        <v>292300</v>
       </c>
       <c r="G81" s="3">
-        <v>-23300</v>
+        <v>-25700</v>
       </c>
       <c r="H81" s="3">
-        <v>65300</v>
+        <v>66200</v>
       </c>
       <c r="I81" s="3">
-        <v>208200</v>
+        <v>215300</v>
       </c>
       <c r="J81" s="3">
-        <v>-34300</v>
+        <v>-37200</v>
       </c>
       <c r="K81" s="3">
         <v>-4300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>325600</v>
+        <v>316100</v>
       </c>
       <c r="E83" s="3">
-        <v>317900</v>
+        <v>296000</v>
       </c>
       <c r="F83" s="3">
-        <v>295700</v>
+        <v>303700</v>
       </c>
       <c r="G83" s="3">
-        <v>286900</v>
+        <v>316800</v>
       </c>
       <c r="H83" s="3">
-        <v>283500</v>
+        <v>287300</v>
       </c>
       <c r="I83" s="3">
-        <v>218200</v>
+        <v>225600</v>
       </c>
       <c r="J83" s="3">
-        <v>189400</v>
+        <v>205300</v>
       </c>
       <c r="K83" s="3">
         <v>168200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>560400</v>
+        <v>559300</v>
       </c>
       <c r="E89" s="3">
-        <v>498400</v>
+        <v>482000</v>
       </c>
       <c r="F89" s="3">
-        <v>395400</v>
+        <v>406000</v>
       </c>
       <c r="G89" s="3">
-        <v>369900</v>
+        <v>408600</v>
       </c>
       <c r="H89" s="3">
-        <v>495100</v>
+        <v>501600</v>
       </c>
       <c r="I89" s="3">
-        <v>73100</v>
+        <v>75600</v>
       </c>
       <c r="J89" s="3">
-        <v>177200</v>
+        <v>192100</v>
       </c>
       <c r="K89" s="3">
         <v>95500</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-373300</v>
+        <v>-372500</v>
       </c>
       <c r="E91" s="3">
-        <v>-302400</v>
+        <v>-291800</v>
       </c>
       <c r="F91" s="3">
-        <v>-257000</v>
+        <v>-263800</v>
       </c>
       <c r="G91" s="3">
-        <v>-201600</v>
+        <v>-222600</v>
       </c>
       <c r="H91" s="3">
-        <v>-300200</v>
+        <v>-304100</v>
       </c>
       <c r="I91" s="3">
-        <v>-306800</v>
+        <v>-317200</v>
       </c>
       <c r="J91" s="3">
-        <v>-305700</v>
+        <v>-331400</v>
       </c>
       <c r="K91" s="3">
         <v>-385200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-319000</v>
+        <v>-318300</v>
       </c>
       <c r="E94" s="3">
-        <v>-299100</v>
+        <v>-288600</v>
       </c>
       <c r="F94" s="3">
-        <v>-244800</v>
+        <v>-251300</v>
       </c>
       <c r="G94" s="3">
-        <v>-194900</v>
+        <v>-215300</v>
       </c>
       <c r="H94" s="3">
-        <v>-391000</v>
+        <v>-396100</v>
       </c>
       <c r="I94" s="3">
-        <v>-100800</v>
+        <v>-104200</v>
       </c>
       <c r="J94" s="3">
-        <v>-323400</v>
+        <v>-350600</v>
       </c>
       <c r="K94" s="3">
         <v>-396000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-201600</v>
+        <v>-201200</v>
       </c>
       <c r="E100" s="3">
-        <v>-180500</v>
+        <v>-174200</v>
       </c>
       <c r="F100" s="3">
-        <v>-481800</v>
+        <v>-494700</v>
       </c>
       <c r="G100" s="3">
-        <v>111900</v>
+        <v>123500</v>
       </c>
       <c r="H100" s="3">
-        <v>-84200</v>
+        <v>-85300</v>
       </c>
       <c r="I100" s="3">
-        <v>-90800</v>
+        <v>-93900</v>
       </c>
       <c r="J100" s="3">
-        <v>67600</v>
+        <v>73200</v>
       </c>
       <c r="K100" s="3">
         <v>157300</v>
@@ -4455,22 +4455,22 @@
         <v>-1100</v>
       </c>
       <c r="E101" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="F101" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="G101" s="3">
-        <v>-4400</v>
+        <v>-4900</v>
       </c>
       <c r="H101" s="3">
         <v>2200</v>
       </c>
       <c r="I101" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J101" s="3">
-        <v>-7800</v>
+        <v>-8400</v>
       </c>
       <c r="K101" s="3">
         <v>3300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>38800</v>
+        <v>38700</v>
       </c>
       <c r="E102" s="3">
-        <v>21000</v>
+        <v>21400</v>
       </c>
       <c r="F102" s="3">
-        <v>-323400</v>
+        <v>-332100</v>
       </c>
       <c r="G102" s="3">
-        <v>282400</v>
+        <v>311900</v>
       </c>
       <c r="H102" s="3">
-        <v>22200</v>
+        <v>22400</v>
       </c>
       <c r="I102" s="3">
-        <v>-116300</v>
+        <v>-120200</v>
       </c>
       <c r="J102" s="3">
-        <v>-86400</v>
+        <v>-93700</v>
       </c>
       <c r="K102" s="3">
         <v>-140000</v>

--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>CSTM</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8001500</v>
+        <v>7335000</v>
       </c>
       <c r="E8" s="3">
-        <v>8678000</v>
+        <v>7826000</v>
       </c>
       <c r="F8" s="3">
+        <v>8532000</v>
+      </c>
+      <c r="G8" s="3">
         <v>6996500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5973100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6628900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6510200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6288400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5146200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5260200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4139300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4180700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3963800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4174100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7216800</v>
+        <v>6397000</v>
       </c>
       <c r="E9" s="3">
-        <v>7959800</v>
+        <v>6771000</v>
       </c>
       <c r="F9" s="3">
+        <v>7569000</v>
+      </c>
+      <c r="G9" s="3">
         <v>6241300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5373700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5953300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5894200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5622000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4586300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4800800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3593900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3617300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6882300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7599200</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>784800</v>
+        <v>938000</v>
       </c>
       <c r="E10" s="3">
-        <v>718200</v>
+        <v>1055000</v>
       </c>
       <c r="F10" s="3">
+        <v>963000</v>
+      </c>
+      <c r="G10" s="3">
         <v>755100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>599400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>675600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>616000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>666400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>559900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>459400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>545400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>563400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-2918500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-3425200</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>57500</v>
+        <v>49000</v>
       </c>
       <c r="E12" s="3">
-        <v>51300</v>
+        <v>52000</v>
       </c>
       <c r="F12" s="3">
+        <v>46000</v>
+      </c>
+      <c r="G12" s="3">
         <v>44400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>53900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>45800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>43200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>42900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>43100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>39500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>38700</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-32100</v>
+        <v>40000</v>
       </c>
       <c r="E14" s="3">
-        <v>-44900</v>
+        <v>-19000</v>
       </c>
       <c r="F14" s="3">
+        <v>22000</v>
+      </c>
+      <c r="G14" s="3">
         <v>73900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>75800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-248500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>93700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>479800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>45200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>27500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23500</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>284100</v>
+        <v>304000</v>
       </c>
       <c r="E15" s="3">
-        <v>264000</v>
+        <v>300000</v>
       </c>
       <c r="F15" s="3">
+        <v>290000</v>
+      </c>
+      <c r="G15" s="3">
         <v>303700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>316800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>287300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>225600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>205300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6600</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7681000</v>
+        <v>7061000</v>
       </c>
       <c r="E17" s="3">
-        <v>8383000</v>
+        <v>7434000</v>
       </c>
       <c r="F17" s="3">
+        <v>8188000</v>
+      </c>
+      <c r="G17" s="3">
         <v>6431300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5734600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6362900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6328100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5913800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4879200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5695000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3969900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3930700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3675000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4248000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>320500</v>
+        <v>274000</v>
       </c>
       <c r="E18" s="3">
-        <v>295000</v>
+        <v>392000</v>
       </c>
       <c r="F18" s="3">
+        <v>344000</v>
+      </c>
+      <c r="G18" s="3">
         <v>565200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>238500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>266000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>182000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>374600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>266900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-434900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>169400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>250000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>288800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>26500</v>
+        <v>5000</v>
       </c>
       <c r="E20" s="3">
-        <v>16000</v>
+        <v>80000</v>
       </c>
       <c r="F20" s="3">
+        <v>74000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>44000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>48100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>58800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-14700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-87300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-70300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-160800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>578100</v>
+        <v>573000</v>
       </c>
       <c r="E21" s="3">
-        <v>542900</v>
+        <v>612000</v>
       </c>
       <c r="F21" s="3">
+        <v>560000</v>
+      </c>
+      <c r="G21" s="3">
         <v>870000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>511300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>543100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>359500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>521100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>438300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-286500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>210100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>200800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>233900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-232400</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>109400</v>
+        <v>94000</v>
       </c>
       <c r="E22" s="3">
-        <v>106900</v>
+        <v>99000</v>
       </c>
       <c r="F22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="G22" s="3">
         <v>131900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>160200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>156000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>136200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>171700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>199600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>169500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>216600</v>
+        <v>135000</v>
       </c>
       <c r="E23" s="3">
-        <v>216900</v>
+        <v>232000</v>
       </c>
       <c r="F23" s="3">
+        <v>150000</v>
+      </c>
+      <c r="G23" s="3">
         <v>360500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>92000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>254200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>70500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-596100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>102700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>161500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>214100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-239500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>74100</v>
+        <v>75000</v>
       </c>
       <c r="E24" s="3">
-        <v>-112200</v>
+        <v>75000</v>
       </c>
       <c r="F24" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="G24" s="3">
         <v>62500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-20800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>36600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>96100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>74900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-32700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>41800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>50500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>142600</v>
+        <v>60000</v>
       </c>
       <c r="E26" s="3">
-        <v>329200</v>
+        <v>157000</v>
       </c>
       <c r="F26" s="3">
+        <v>315000</v>
+      </c>
+      <c r="G26" s="3">
         <v>298000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>71800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>217500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-37200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-563500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>61000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>114800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>163600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-199500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>138200</v>
+        <v>56000</v>
       </c>
       <c r="E27" s="3">
-        <v>321700</v>
+        <v>152000</v>
       </c>
       <c r="F27" s="3">
+        <v>308000</v>
+      </c>
+      <c r="G27" s="3">
         <v>292300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>66200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>215300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-37200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-565500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>57600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>112400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>161400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200700</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,27 +1670,30 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>4800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-8800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-26500</v>
+        <v>-5000</v>
       </c>
       <c r="E32" s="3">
-        <v>-16000</v>
+        <v>-80000</v>
       </c>
       <c r="F32" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-44000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-48100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-58800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>14700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>87300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>70300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>160800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>138200</v>
+        <v>56000</v>
       </c>
       <c r="E33" s="3">
-        <v>321700</v>
+        <v>152000</v>
       </c>
       <c r="F33" s="3">
+        <v>308000</v>
+      </c>
+      <c r="G33" s="3">
         <v>292300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>66200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>215300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-37200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-565500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>57600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>117200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>152600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>138200</v>
+        <v>56000</v>
       </c>
       <c r="E35" s="3">
-        <v>321700</v>
+        <v>152000</v>
       </c>
       <c r="F35" s="3">
+        <v>308000</v>
+      </c>
+      <c r="G35" s="3">
         <v>292300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>66200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>215300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-37200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-565500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>57600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>117200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>152600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>223300</v>
+        <v>141000</v>
       </c>
       <c r="E41" s="3">
+        <v>223000</v>
+      </c>
+      <c r="F41" s="3">
         <v>177400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>167200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>537000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>206500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>187800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>323000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>376500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>481800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>189700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>277500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>153700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>120900</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2065,200 +2154,215 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>927000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>49300</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>532800</v>
+        <v>486000</v>
       </c>
       <c r="E43" s="3">
+        <v>531000</v>
+      </c>
+      <c r="F43" s="3">
         <v>567500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>766500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>489300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>522900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>660600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>495900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>375400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>370600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>637900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>574200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1042000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>616300</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1213700</v>
+        <v>1181000</v>
       </c>
       <c r="E44" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1410700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1194100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>711900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>751900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>755700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>772100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>641200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>553300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>487800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>392400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>422700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>495300</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33200</v>
+        <v>26000</v>
       </c>
       <c r="E45" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F45" s="3">
         <v>48100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>66000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>47700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>80500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>136700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>86800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>83600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2011700</v>
+        <v>1834000</v>
       </c>
       <c r="E46" s="3">
+        <v>1992000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2212200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2204000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1793300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1515000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1649900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1681100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1529800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1492400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2325900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1303900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1138600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1293500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2274,126 +2378,135 @@
       <c r="G47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="3">
-        <v>1100</v>
+      <c r="H47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="I47" s="3">
         <v>1100</v>
       </c>
       <c r="J47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>84700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>81300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>83400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>111500</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2262600</v>
+        <v>2408000</v>
       </c>
       <c r="E48" s="3">
+        <v>2422000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2155600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2215400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2331500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2307300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1907500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1821600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1602500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1281100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>713600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>488000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>663200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>232400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>562600</v>
+        <v>143000</v>
       </c>
       <c r="E49" s="3">
+        <v>145000</v>
+      </c>
+      <c r="F49" s="3">
         <v>568600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>578900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>584700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>589200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>563300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>565600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>581600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>531800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>31600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>25100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18800</v>
+        <v>22000</v>
       </c>
       <c r="E52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F52" s="3">
         <v>38500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>54600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>77100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>49200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>326600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>313400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>268700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>211700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>225100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>240600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5152000</v>
+        <v>4734000</v>
       </c>
       <c r="E54" s="3">
+        <v>4933000</v>
+      </c>
+      <c r="F54" s="3">
         <v>5280500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5258700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5050800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4695300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4466500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4456100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4108900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3703500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3400800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2110100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1790800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1892200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1029100</v>
+        <v>959000</v>
       </c>
       <c r="E57" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1234400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1211200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>765700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>797900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>784300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>861000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>680300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>670700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>744100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>561000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>965100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>544600</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>59700</v>
+        <v>56000</v>
       </c>
       <c r="E58" s="3">
+        <v>59000</v>
+      </c>
+      <c r="F58" s="3">
         <v>158200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>293400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>126000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>230100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>68700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>132100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>116100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>172500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>53100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>19800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>85700</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>195600</v>
+        <v>227000</v>
       </c>
       <c r="E59" s="3">
+        <v>239000</v>
+      </c>
+      <c r="F59" s="3">
         <v>200900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>216100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>243400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>191900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>249600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>134500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>326600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>387900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>397400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>319400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>269000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>410800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1534200</v>
+        <v>1446000</v>
       </c>
       <c r="E60" s="3">
+        <v>1556000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1820000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1949300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1328400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1427400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1304100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1332900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1123000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1231100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1194600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>906700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>818000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>987200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2005100</v>
+        <v>1974000</v>
       </c>
       <c r="E61" s="3">
+        <v>1995000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2039100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2127800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2853800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2429600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2410100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2471200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2561700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2106900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1360600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>390000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>153700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>165500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>140400</v>
+        <v>140000</v>
       </c>
       <c r="E62" s="3">
+        <v>142000</v>
+      </c>
+      <c r="F62" s="3">
         <v>135700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>149000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>163900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>148100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>148800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>166900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1042700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>916700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>887500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>770400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>859700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1172600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4197000</v>
+        <v>4007000</v>
       </c>
       <c r="E66" s="3">
+        <v>4191000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4476900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4927800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5174300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4790700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4597000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4839100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4737100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4265900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3449400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2071800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1835900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2027200</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>302900</v>
+        <v>93000</v>
       </c>
       <c r="E72" s="3">
+        <v>65000</v>
+      </c>
+      <c r="F72" s="3">
         <v>158200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-174000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-501500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-436500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-512900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-761300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-799600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-736000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-208900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-141200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-289900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-233600</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>931800</v>
+        <v>706000</v>
       </c>
       <c r="E76" s="3">
+        <v>718000</v>
+      </c>
+      <c r="F76" s="3">
         <v>781200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>311600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-140700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-107700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-139700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-392700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-628200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-562500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-48600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-45000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-135000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>138200</v>
+        <v>56000</v>
       </c>
       <c r="E81" s="3">
-        <v>321700</v>
+        <v>152000</v>
       </c>
       <c r="F81" s="3">
+        <v>308000</v>
+      </c>
+      <c r="G81" s="3">
         <v>292300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>66200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>215300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-37200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-565500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>57600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>117200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>152600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>316100</v>
+        <v>304000</v>
       </c>
       <c r="E83" s="3">
-        <v>296000</v>
+        <v>300000</v>
       </c>
       <c r="F83" s="3">
+        <v>290000</v>
+      </c>
+      <c r="G83" s="3">
         <v>303700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>316800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>287300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>225600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>205300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>168200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>142900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2300</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>559300</v>
+        <v>301000</v>
       </c>
       <c r="E89" s="3">
-        <v>482000</v>
+        <v>432000</v>
       </c>
       <c r="F89" s="3">
+        <v>365000</v>
+      </c>
+      <c r="G89" s="3">
         <v>406000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>408600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>501600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>75600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>192100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>95500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>521600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>239400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>220100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>270100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-372500</v>
+        <v>-413000</v>
       </c>
       <c r="E91" s="3">
-        <v>-291800</v>
+        <v>-366000</v>
       </c>
       <c r="F91" s="3">
+        <v>-289000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-263800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-222600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-304100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-317200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-331400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-385200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-357300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-224700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-172300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-138300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-113900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-318300</v>
+        <v>-313000</v>
       </c>
       <c r="E94" s="3">
-        <v>-288600</v>
+        <v>-216000</v>
       </c>
       <c r="F94" s="3">
+        <v>-196000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-251300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-215300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-396100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-104200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-350600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-396000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-737000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-243900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-157900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-143800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4257,17 +4490,20 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-175800</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-201200</v>
+        <v>-61000</v>
       </c>
       <c r="E100" s="3">
-        <v>-174200</v>
+        <v>-177000</v>
       </c>
       <c r="F100" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-494700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>123500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-85300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-93900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>73200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>157300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-314400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>850200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>51400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-94400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>235900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1100</v>
+        <v>-9000</v>
       </c>
       <c r="E101" s="3">
-        <v>2100</v>
+        <v>7000</v>
       </c>
       <c r="F101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>11700</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>38700</v>
+        <v>-82000</v>
       </c>
       <c r="E102" s="3">
-        <v>21400</v>
+        <v>46000</v>
       </c>
       <c r="F102" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-332100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>311900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>22400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-120200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-93700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-140000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-525700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>852500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>112400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>132600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>CSTM</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8449000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7335000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7826000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8532000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6996500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5973100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6628900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6510200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6288400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5146200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5260200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4139300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4180700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3963800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4174100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6397000</v>
+        <v>7238000</v>
       </c>
       <c r="E9" s="3">
-        <v>6771000</v>
+        <v>6374000</v>
       </c>
       <c r="F9" s="3">
-        <v>7569000</v>
+        <v>6747000</v>
       </c>
       <c r="G9" s="3">
+        <v>7545000</v>
+      </c>
+      <c r="H9" s="3">
         <v>6241300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5373700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5953300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5894200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5622000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4586300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4800800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3593900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3617300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6882300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7599200</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>938000</v>
+        <v>1211000</v>
       </c>
       <c r="E10" s="3">
-        <v>1055000</v>
+        <v>961000</v>
       </c>
       <c r="F10" s="3">
-        <v>963000</v>
+        <v>1079000</v>
       </c>
       <c r="G10" s="3">
+        <v>987000</v>
+      </c>
+      <c r="H10" s="3">
         <v>755100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>599400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>675600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>616000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>666400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>559900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>459400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>545400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>563400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2918500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-3425200</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E12" s="3">
         <v>49000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>46000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>44400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>47700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>53900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>45800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>43200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>34700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>35700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>42900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>43100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>39500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>38700</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="E14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-19000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>73900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>75800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-248500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>93700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>479800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>45200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>27500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23500</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E15" s="3">
         <v>304000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>300000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>290000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>303700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>316800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>287300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>225600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>205300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6600</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7968000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7061000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7434000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8188000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6431300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5734600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6362900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6328100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5913800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4879200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5695000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3969900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3930700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3675000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4248000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>481000</v>
+      </c>
+      <c r="E18" s="3">
         <v>274000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>392000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>344000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>565200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>238500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>266000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>182000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>374600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>266900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-434900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>169400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>250000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>288800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-74000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5000</v>
+        <v>-54000</v>
       </c>
       <c r="E20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F20" s="3">
         <v>80000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>74000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>44000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>48100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>58800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-14700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-87300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-70300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-160800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>573000</v>
+        <v>865000</v>
       </c>
       <c r="E21" s="3">
+        <v>566000</v>
+      </c>
+      <c r="F21" s="3">
         <v>612000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>560000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>870000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>511300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>543100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>359500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>521100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>438300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-286500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>210100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>233900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-232400</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E22" s="3">
         <v>94000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>99000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>98000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>131900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>160200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>156000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>136200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>171700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>199600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>169500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>408000</v>
+      </c>
+      <c r="E23" s="3">
         <v>135000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>232000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>150000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>360500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>92000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>254200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>70500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-596100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>102700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>161500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>214100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-239500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>75000</v>
+        <v>133000</v>
       </c>
       <c r="E24" s="3">
         <v>75000</v>
       </c>
       <c r="F24" s="3">
+        <v>75000</v>
+      </c>
+      <c r="G24" s="3">
         <v>-165000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>62500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-20800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>36600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>96100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-32700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>41800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>46700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>50500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-39900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E26" s="3">
         <v>60000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>157000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>315000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>298000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>71800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>217500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-37200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-563500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>61000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>114800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>163600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-199500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E27" s="3">
         <v>56000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>152000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>308000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>292300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>66200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>215300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-37200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-565500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>57600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>161400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200700</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,27 +1733,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>4800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-9400</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5000</v>
+        <v>54000</v>
       </c>
       <c r="E32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-80000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-74000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-44000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-48100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-58800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>14700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>87300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>70300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>160800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E33" s="3">
         <v>56000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>152000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>308000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>292300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>66200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>215300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-37200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-565500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>57600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>117200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>152600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-210100</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E35" s="3">
         <v>56000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>152000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>308000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>292300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>66200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>215300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-37200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-565500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>57600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>117200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>152600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-210100</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E41" s="3">
         <v>141000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>223000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>177400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>167200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>537000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>206500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>187800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>323000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>376500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>481800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>189700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>277500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>153700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>120900</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2157,212 +2246,227 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>927000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>31100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>49300</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>723000</v>
+      </c>
+      <c r="E43" s="3">
         <v>486000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>531000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>567500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>766500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>489300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>522900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>660600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>495900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>375400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>370600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>637900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>574200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1042000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>616300</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1407000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1181000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1197000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1410700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1194100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>711900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>751900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>755700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>772100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>641200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>553300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>487800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>392400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>422700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>495300</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E45" s="3">
         <v>26000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>66000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>47700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>80500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>136700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>86800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>83600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2322000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1834000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1992000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2212200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2204000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1793300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1515000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1649900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1681100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1529800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1492400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2325900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1303900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1138600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1293500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2381,132 +2485,141 @@
       <c r="H47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I47" s="3">
-        <v>1100</v>
+      <c r="I47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="J47" s="3">
         <v>1100</v>
       </c>
       <c r="K47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L47" s="3">
         <v>1200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>84700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>81300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>83400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>111500</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2585000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2408000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2422000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2155600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2215400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2331500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2307300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1907500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1821600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1602500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1281100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>713600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>488000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>663200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>232400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E49" s="3">
         <v>143000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>145000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>568600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>578900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>584700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>589200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>563300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>565600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>581600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>531800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>31600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>27000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="E52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F52" s="3">
         <v>20000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>54600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>77100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>49200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>51600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>326600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>313400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>268700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>211700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>225100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>240600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5354000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4734000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4933000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5280500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5258700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5050800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4695300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4466500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4456100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4108900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3703500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3400800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2110100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1790800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1892200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1222000</v>
+      </c>
+      <c r="E57" s="3">
         <v>959000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1025000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1234400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1211200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>765700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>797900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>784300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>861000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>680300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>670700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>744100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>561000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>965100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>544600</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E58" s="3">
         <v>56000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>59000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>158200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>293400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>126000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>230100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>68700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>132100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>116100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>172500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>53100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>26300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>19800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>85700</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E59" s="3">
         <v>227000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>239000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>200900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>216100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>243400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>191900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>249600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>134500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>326600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>387900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>397400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>319400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>269000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>410800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1446000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1556000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1820000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1949300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1328400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1427400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1304100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1332900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1123000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1231100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1194600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>906700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>818000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>987200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2003000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1974000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1995000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2039100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2127800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2853800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2429600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2410100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2471200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2561700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2106900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1360600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>390000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>153700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>165500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>140000</v>
+        <v>174000</v>
       </c>
       <c r="E62" s="3">
+        <v>173000</v>
+      </c>
+      <c r="F62" s="3">
         <v>142000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>135700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>149000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>163900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>148100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>148800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>166900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1042700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>916700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>887500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>770400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>859700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1172600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4383000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4007000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4191000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4476900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4927800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5174300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4790700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4597000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4839100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4737100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4265900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3449400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2071800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1835900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2027200</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>354000</v>
+      </c>
+      <c r="E72" s="3">
         <v>93000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>65000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>158200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-174000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-501500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-436500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-512900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-761300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-799600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-736000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-208900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-141200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-289900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-233600</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>952000</v>
+      </c>
+      <c r="E76" s="3">
         <v>706000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>718000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>781200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>311600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-140700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-107700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-139700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-392700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-628200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-562500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-48600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-135000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E81" s="3">
         <v>56000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>152000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>308000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>292300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>66200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>215300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-37200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-565500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>57600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>117200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>152600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-210100</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>304000</v>
+        <v>316000</v>
       </c>
       <c r="E83" s="3">
-        <v>300000</v>
+        <v>291000</v>
       </c>
       <c r="F83" s="3">
+        <v>286000</v>
+      </c>
+      <c r="G83" s="3">
         <v>290000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>303700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>316800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>287300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>225600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>205300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>168200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>142900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>55300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2300</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E89" s="3">
         <v>301000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>432000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>365000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>406000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>408600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>501600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>75600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>192100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>95500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>521600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>239400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>220100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>270100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-34000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-330000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-413000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-366000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-289000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-263800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-222600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-304100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-317200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-331400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-385200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-357300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-224700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-172300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-138300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-113900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-309000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-313000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-216000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-196000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-251300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-215300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-396100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-104200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-350600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-396000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-737000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-243900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-157900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-143800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-81000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,8 +4686,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4493,17 +4726,20 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-175800</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-61000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-177000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-150000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-494700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>123500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-85300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-93900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>73200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>157300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-314400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>850200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>51400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-94400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>235900</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>11700</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-82000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-332100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>311900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-120200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-93700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-140000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-525700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>852500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>112400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>31800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>132600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -4099,7 +4099,7 @@
         <v>286000</v>
       </c>
       <c r="G83" s="3">
-        <v>290000</v>
+        <v>275000</v>
       </c>
       <c r="H83" s="3">
         <v>303700</v>
